--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Download\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git-Folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D88795-4CF9-4D01-B569-6618B4A2ED01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F906175-95C4-4F47-91F9-FCFFF87F568E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4770" yWindow="390" windowWidth="21600" windowHeight="8475" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions 2(Records)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="57">
   <si>
     <t>Goals</t>
   </si>
@@ -168,6 +168,42 @@
   </si>
   <si>
     <t>Current Profit/Loss:</t>
+  </si>
+  <si>
+    <t>Forgot to Place</t>
+  </si>
+  <si>
+    <t>Match Week 9</t>
+  </si>
+  <si>
+    <t>LEE vs WHU</t>
+  </si>
+  <si>
+    <t>CHE vs SUN</t>
+  </si>
+  <si>
+    <t>NCU vs FUL</t>
+  </si>
+  <si>
+    <t>MUN vs BHA</t>
+  </si>
+  <si>
+    <t>BRE vs LIV</t>
+  </si>
+  <si>
+    <t>BOU vs NOF</t>
+  </si>
+  <si>
+    <t>ARS vs CRY</t>
+  </si>
+  <si>
+    <t>AVL vs MCI</t>
+  </si>
+  <si>
+    <t>WOL vs BUR</t>
+  </si>
+  <si>
+    <t>EVE vs TOT</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1212,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA341253-1EAB-4104-BE4B-374BC158237A}">
-  <dimension ref="A1:W51"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" ht="24" x14ac:dyDescent="0.4">
@@ -2295,31 +2331,31 @@
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I42" s="5"/>
       <c r="J42" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="K42" s="5"/>
       <c r="L42" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="M42" s="5"/>
       <c r="N42" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="O42" s="5"/>
       <c r="P42" s="5" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5" t="s">
@@ -2348,7 +2384,7 @@
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I43" s="5"/>
       <c r="J43" s="5">
@@ -2356,7 +2392,7 @@
       </c>
       <c r="K43" s="5"/>
       <c r="L43" s="5">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="M43" s="5"/>
       <c r="N43" s="5">
@@ -2375,7 +2411,7 @@
         <v>3.5</v>
       </c>
       <c r="U43" s="5"/>
-      <c r="V43" s="5">
+      <c r="V43" s="6">
         <v>3.5</v>
       </c>
     </row>
@@ -2384,25 +2420,45 @@
         <v>16</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
+      <c r="D44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
+      <c r="F44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="H44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="I44" s="5"/>
-      <c r="J44" s="5"/>
+      <c r="J44" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K44" s="5"/>
-      <c r="L44" s="5"/>
+      <c r="L44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="M44" s="5"/>
-      <c r="N44" s="5"/>
+      <c r="N44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="O44" s="5"/>
-      <c r="P44" s="5"/>
+      <c r="P44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="Q44" s="5"/>
-      <c r="R44" s="5"/>
+      <c r="R44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="S44" s="5"/>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="U44" s="5"/>
-      <c r="V44" s="6"/>
+      <c r="V44" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B45" s="4" t="s">
@@ -2454,33 +2510,19 @@
         <v>18</v>
       </c>
       <c r="C47" s="5"/>
-      <c r="D47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="D47" s="5"/>
       <c r="E47" s="5"/>
-      <c r="F47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="F47" s="5"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="H47" s="5"/>
       <c r="I47" s="5"/>
-      <c r="J47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="J47" s="5"/>
       <c r="K47" s="5"/>
-      <c r="L47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="L47" s="5"/>
       <c r="M47" s="5"/>
-      <c r="N47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="N47" s="5"/>
       <c r="O47" s="5"/>
-      <c r="P47" s="5">
-        <v>-1</v>
-      </c>
+      <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
       <c r="R47" s="5">
         <v>-1</v>
@@ -2495,7 +2537,7 @@
       </c>
       <c r="W47" s="8">
         <f>SUM(D47:V47)</f>
-        <v>-10</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="48" spans="1:23" x14ac:dyDescent="0.25">
@@ -2505,37 +2547,37 @@
       <c r="C48" s="5"/>
       <c r="D48" s="5">
         <f>IF(D45&gt;0,ROUND(ABS(D47)*(D45/100),2),ROUND(D47/(D45/100),2))</f>
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5">
         <f>IF(F45&gt;0,ROUND(ABS(F47)*(F45/100),2),ROUND(F47/(F45/100),2))</f>
-        <v>0.42</v>
+        <v>0</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5">
         <f>IF(H45&gt;0,ROUND(ABS(H47)*(H45/100),2),ROUND(H47/(H45/100),2))</f>
-        <v>1.1499999999999999</v>
+        <v>0</v>
       </c>
       <c r="I48" s="5"/>
       <c r="J48" s="5">
         <f>IF(J45&gt;0,ROUND(ABS(J47)*(J45/100),2),ROUND(J47/(J45/100),2))</f>
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="K48" s="5"/>
       <c r="L48" s="5">
         <f>IF(L45&gt;0,ROUND(ABS(L47)*(L45/100),2),ROUND(L47/(L45/100),2))</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" s="5">
         <f>IF(N45&gt;0,ROUND(ABS(N47)*(N45/100),2),ROUND(N47/(N45/100),2))</f>
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="O48" s="5"/>
       <c r="P48" s="5">
         <f>IF(P45&gt;0,ROUND(ABS(P47)*(P45/100),2),ROUND(P47/(P45/100),2))</f>
-        <v>0.28999999999999998</v>
+        <v>0</v>
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5">
@@ -2554,10 +2596,10 @@
       </c>
       <c r="W48" s="8">
         <f>SUM(D48:V48)</f>
-        <v>6.71</v>
-      </c>
-    </row>
-    <row r="49" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
         <v>20</v>
       </c>
@@ -2599,41 +2641,573 @@
       <c r="Q49" s="5"/>
       <c r="R49" s="5">
         <f>IF(R44=R42,-R47+R48,0)</f>
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S49" s="5"/>
       <c r="T49" s="5">
         <f>IF(T44=T42,-T47+T48,0)</f>
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="U49" s="5"/>
       <c r="V49" s="6">
         <f>IF(V44=V42,-V47+V48,0)</f>
-        <v>0</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="W49" s="9">
         <f>SUM(D49:V49)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="50" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="W50" s="7">
         <f>W47+W49</f>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="51" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.4000000000000004</v>
+      </c>
+    </row>
+    <row r="51" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="U51" s="12" t="s">
         <v>44</v>
       </c>
       <c r="V51" s="12"/>
       <c r="W51" s="11">
         <f>W34+W50</f>
-        <v>-10.58</v>
+        <v>0.82000000000000028</v>
+      </c>
+    </row>
+    <row r="52" spans="1:23" ht="24" x14ac:dyDescent="0.4">
+      <c r="D52" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13"/>
+    </row>
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D53" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" t="s">
+        <v>48</v>
+      </c>
+      <c r="H53" t="s">
+        <v>49</v>
+      </c>
+      <c r="J53" t="s">
+        <v>50</v>
+      </c>
+      <c r="L53" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" t="s">
+        <v>52</v>
+      </c>
+      <c r="P53" t="s">
+        <v>53</v>
+      </c>
+      <c r="R53" t="s">
+        <v>54</v>
+      </c>
+      <c r="T53" t="s">
+        <v>55</v>
+      </c>
+      <c r="V53" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>3.5</v>
+      </c>
+      <c r="B54" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D54" t="s">
+        <v>14</v>
+      </c>
+      <c r="F54" t="s">
+        <v>13</v>
+      </c>
+      <c r="H54" t="s">
+        <v>13</v>
+      </c>
+      <c r="J54" t="s">
+        <v>13</v>
+      </c>
+      <c r="L54" t="s">
+        <v>13</v>
+      </c>
+      <c r="N54" t="s">
+        <v>13</v>
+      </c>
+      <c r="P54" t="s">
+        <v>13</v>
+      </c>
+      <c r="R54" t="s">
+        <v>13</v>
+      </c>
+      <c r="T54" t="s">
+        <v>13</v>
+      </c>
+      <c r="V54" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2.5</v>
+      </c>
+      <c r="B55" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D55" t="s">
+        <v>14</v>
+      </c>
+      <c r="F55" t="s">
+        <v>13</v>
+      </c>
+      <c r="H55" t="s">
+        <v>13</v>
+      </c>
+      <c r="J55" t="s">
+        <v>13</v>
+      </c>
+      <c r="L55" t="s">
+        <v>13</v>
+      </c>
+      <c r="N55" t="s">
+        <v>13</v>
+      </c>
+      <c r="P55" t="s">
+        <v>13</v>
+      </c>
+      <c r="R55" t="s">
+        <v>13</v>
+      </c>
+      <c r="T55" t="s">
+        <v>13</v>
+      </c>
+      <c r="V55" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A56">
+        <v>3.5</v>
+      </c>
+      <c r="B56" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D56" t="s">
+        <v>14</v>
+      </c>
+      <c r="F56" t="s">
+        <v>13</v>
+      </c>
+      <c r="H56" t="s">
+        <v>13</v>
+      </c>
+      <c r="J56" t="s">
+        <v>13</v>
+      </c>
+      <c r="L56" t="s">
+        <v>13</v>
+      </c>
+      <c r="N56" t="s">
+        <v>13</v>
+      </c>
+      <c r="P56" t="s">
+        <v>13</v>
+      </c>
+      <c r="R56" t="s">
+        <v>13</v>
+      </c>
+      <c r="T56" t="s">
+        <v>13</v>
+      </c>
+      <c r="V56" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>2.5</v>
+      </c>
+      <c r="B57" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D57" t="s">
+        <v>14</v>
+      </c>
+      <c r="F57" t="s">
+        <v>13</v>
+      </c>
+      <c r="H57" t="s">
+        <v>13</v>
+      </c>
+      <c r="J57" t="s">
+        <v>13</v>
+      </c>
+      <c r="L57" t="s">
+        <v>13</v>
+      </c>
+      <c r="N57" t="s">
+        <v>13</v>
+      </c>
+      <c r="P57" t="s">
+        <v>13</v>
+      </c>
+      <c r="R57" t="s">
+        <v>13</v>
+      </c>
+      <c r="T57" t="s">
+        <v>13</v>
+      </c>
+      <c r="V57" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B59" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K59" s="5"/>
+      <c r="L59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M59" s="5"/>
+      <c r="N59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O59" s="5"/>
+      <c r="P59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q59" s="5"/>
+      <c r="R59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S59" s="5"/>
+      <c r="T59" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="U59" s="5"/>
+      <c r="V59" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B60" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C60" s="5"/>
+      <c r="D60" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="G60" s="5"/>
+      <c r="H60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="I60" s="5"/>
+      <c r="J60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="K60" s="5"/>
+      <c r="L60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="M60" s="5"/>
+      <c r="N60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="O60" s="5"/>
+      <c r="P60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="Q60" s="5"/>
+      <c r="R60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="S60" s="5"/>
+      <c r="T60" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="U60" s="5"/>
+      <c r="V60" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B61" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+      <c r="I61" s="5"/>
+      <c r="J61" s="5"/>
+      <c r="K61" s="5"/>
+      <c r="L61" s="5"/>
+      <c r="M61" s="5"/>
+      <c r="N61" s="5"/>
+      <c r="O61" s="5"/>
+      <c r="P61" s="5"/>
+      <c r="Q61" s="5"/>
+      <c r="R61" s="5"/>
+      <c r="S61" s="5"/>
+      <c r="T61" s="5"/>
+      <c r="U61" s="5"/>
+      <c r="V61" s="6"/>
+    </row>
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B62" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+      <c r="I62" s="5"/>
+      <c r="J62" s="5"/>
+      <c r="K62" s="5"/>
+      <c r="L62" s="5"/>
+      <c r="M62" s="5"/>
+      <c r="N62" s="5"/>
+      <c r="O62" s="5"/>
+      <c r="P62" s="5"/>
+      <c r="Q62" s="5"/>
+      <c r="R62" s="5"/>
+      <c r="S62" s="5"/>
+      <c r="T62" s="5"/>
+      <c r="U62" s="5"/>
+      <c r="V62" s="6"/>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C64" s="5"/>
+      <c r="D64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G64" s="5"/>
+      <c r="H64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="K64" s="5"/>
+      <c r="L64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="M64" s="5"/>
+      <c r="N64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="O64" s="5"/>
+      <c r="P64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q64" s="5"/>
+      <c r="R64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S64" s="5"/>
+      <c r="T64" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U64" s="5"/>
+      <c r="V64" s="6">
+        <v>-1</v>
+      </c>
+      <c r="W64" s="8">
+        <f>SUM(D64:V64)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B65" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C65" s="5"/>
+      <c r="D65" s="5" t="e">
+        <f>IF(D62&gt;0,ROUND(ABS(D64)*(D62/100),2),ROUND(D64/(D62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5" t="e">
+        <f>IF(F62&gt;0,ROUND(ABS(F64)*(F62/100),2),ROUND(F64/(F62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G65" s="5"/>
+      <c r="H65" s="5" t="e">
+        <f>IF(H62&gt;0,ROUND(ABS(H64)*(H62/100),2),ROUND(H64/(H62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="5"/>
+      <c r="J65" s="5" t="e">
+        <f>IF(J62&gt;0,ROUND(ABS(J64)*(J62/100),2),ROUND(J64/(J62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K65" s="5"/>
+      <c r="L65" s="5" t="e">
+        <f>IF(L62&gt;0,ROUND(ABS(L64)*(L62/100),2),ROUND(L64/(L62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M65" s="5"/>
+      <c r="N65" s="5" t="e">
+        <f>IF(N62&gt;0,ROUND(ABS(N64)*(N62/100),2),ROUND(N64/(N62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O65" s="5"/>
+      <c r="P65" s="5" t="e">
+        <f>IF(P62&gt;0,ROUND(ABS(P64)*(P62/100),2),ROUND(P64/(P62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q65" s="5"/>
+      <c r="R65" s="5" t="e">
+        <f>IF(R62&gt;0,ROUND(ABS(R64)*(R62/100),2),ROUND(R64/(R62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S65" s="5"/>
+      <c r="T65" s="5" t="e">
+        <f>IF(T62&gt;0,ROUND(ABS(T64)*(T62/100),2),ROUND(T64/(T62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U65" s="5"/>
+      <c r="V65" s="5" t="e">
+        <f>IF(V62&gt;0,ROUND(ABS(V64)*(V62/100),2),ROUND(V64/(V62/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W65" s="8" t="e">
+        <f>SUM(D65:V65)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B66" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" s="5"/>
+      <c r="D66" s="5">
+        <f>IF(D61=D59,-D64+D65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5">
+        <f>IF(F61=F59,-F64+F65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G66" s="5"/>
+      <c r="H66" s="5">
+        <f>IF(H61=H59,-H64+H65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5">
+        <f>IF(J61=J59,-J64+J65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K66" s="5"/>
+      <c r="L66" s="5">
+        <f>IF(L61=L59,-L64+L65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M66" s="5"/>
+      <c r="N66" s="5">
+        <f>IF(N61=N59,-N64+N65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O66" s="5"/>
+      <c r="P66" s="5">
+        <f>IF(P61=P59,-P64+P65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q66" s="5"/>
+      <c r="R66" s="5">
+        <f>IF(R61=R59,-R64+R65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S66" s="5"/>
+      <c r="T66" s="5">
+        <f>IF(T61=T59,-T64+T65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U66" s="5"/>
+      <c r="V66" s="6">
+        <f>IF(V61=V59,-V64+V65,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W66" s="9">
+        <f>SUM(D66:V66)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W67" s="7">
+        <f>W64+W66</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U68" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="V68" s="12"/>
+      <c r="W68" s="11" t="e">
+        <f>#REF!+W67</f>
+        <v>#REF!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
+    <mergeCell ref="D52:V52"/>
+    <mergeCell ref="U68:V68"/>
     <mergeCell ref="U51:V51"/>
     <mergeCell ref="D1:V1"/>
     <mergeCell ref="D18:V18"/>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git-Folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F906175-95C4-4F47-91F9-FCFFF87F568E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF32F3-9BBB-4C84-8EF9-6C5B62D3904E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="68">
   <si>
     <t>Goals</t>
   </si>
@@ -204,6 +204,39 @@
   </si>
   <si>
     <t>EVE vs TOT</t>
+  </si>
+  <si>
+    <t>Match Week 10</t>
+  </si>
+  <si>
+    <t>BHA vs LEE</t>
+  </si>
+  <si>
+    <t>CRY vs BRE</t>
+  </si>
+  <si>
+    <t>FUL vs WOL</t>
+  </si>
+  <si>
+    <t>BUR vs ARS</t>
+  </si>
+  <si>
+    <t>NOF vs MUN</t>
+  </si>
+  <si>
+    <t>TOT vs CHE</t>
+  </si>
+  <si>
+    <t>LIV vs AVL</t>
+  </si>
+  <si>
+    <t>WHU vs NCU</t>
+  </si>
+  <si>
+    <t>MCI vs BOU</t>
+  </si>
+  <si>
+    <t>SUN vs EVE</t>
   </si>
 </sst>
 </file>
@@ -831,10 +864,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1212,34 +1245,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA341253-1EAB-4104-BE4B-374BC158237A}">
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" ht="24" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="13"/>
-      <c r="M1" s="13"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="13"/>
-      <c r="P1" s="13"/>
-      <c r="Q1" s="13"/>
-      <c r="R1" s="13"/>
-      <c r="S1" s="13"/>
-      <c r="T1" s="13"/>
-      <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="12"/>
+      <c r="N1" s="12"/>
+      <c r="O1" s="12"/>
+      <c r="P1" s="12"/>
+      <c r="Q1" s="12"/>
+      <c r="R1" s="12"/>
+      <c r="S1" s="12"/>
+      <c r="T1" s="12"/>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
@@ -1639,37 +1672,37 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U17" s="12" t="s">
+      <c r="U17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V17" s="12"/>
+      <c r="V17" s="13"/>
       <c r="W17" s="11">
         <f>W16</f>
         <v>-0.74000000000000021</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="13"/>
-      <c r="Q18" s="13"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="13"/>
-      <c r="T18" s="13"/>
-      <c r="U18" s="13"/>
-      <c r="V18" s="13"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
@@ -2109,37 +2142,37 @@
       </c>
     </row>
     <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U34" s="12" t="s">
+      <c r="U34" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V34" s="12"/>
+      <c r="V34" s="13"/>
       <c r="W34" s="11">
         <f>W33+W17</f>
         <v>-0.58000000000000007</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="13"/>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
-      <c r="K35" s="13"/>
-      <c r="L35" s="13"/>
-      <c r="M35" s="13"/>
-      <c r="N35" s="13"/>
-      <c r="O35" s="13"/>
-      <c r="P35" s="13"/>
-      <c r="Q35" s="13"/>
-      <c r="R35" s="13"/>
-      <c r="S35" s="13"/>
-      <c r="T35" s="13"/>
-      <c r="U35" s="13"/>
-      <c r="V35" s="13"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
@@ -2665,37 +2698,37 @@
       </c>
     </row>
     <row r="51" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U51" s="12" t="s">
+      <c r="U51" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V51" s="12"/>
+      <c r="V51" s="13"/>
       <c r="W51" s="11">
         <f>W34+W50</f>
         <v>0.82000000000000028</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D52" s="13" t="s">
+      <c r="D52" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="13"/>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="13"/>
-      <c r="K52" s="13"/>
-      <c r="L52" s="13"/>
-      <c r="M52" s="13"/>
-      <c r="N52" s="13"/>
-      <c r="O52" s="13"/>
-      <c r="P52" s="13"/>
-      <c r="Q52" s="13"/>
-      <c r="R52" s="13"/>
-      <c r="S52" s="13"/>
-      <c r="T52" s="13"/>
-      <c r="U52" s="13"/>
-      <c r="V52" s="13"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="12"/>
+      <c r="H52" s="12"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="12"/>
+      <c r="Q52" s="12"/>
+      <c r="R52" s="12"/>
+      <c r="S52" s="12"/>
+      <c r="T52" s="12"/>
+      <c r="U52" s="12"/>
+      <c r="V52" s="12"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
@@ -2976,50 +3009,90 @@
         <v>16</v>
       </c>
       <c r="C61" s="5"/>
-      <c r="D61" s="5"/>
+      <c r="D61" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="E61" s="5"/>
-      <c r="F61" s="5"/>
+      <c r="F61" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="I61" s="5"/>
-      <c r="J61" s="5"/>
+      <c r="J61" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K61" s="5"/>
-      <c r="L61" s="5"/>
+      <c r="L61" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="M61" s="5"/>
-      <c r="N61" s="5"/>
+      <c r="N61" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="O61" s="5"/>
-      <c r="P61" s="5"/>
+      <c r="P61" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="Q61" s="5"/>
-      <c r="R61" s="5"/>
+      <c r="R61" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="S61" s="5"/>
-      <c r="T61" s="5"/>
+      <c r="T61" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="U61" s="5"/>
-      <c r="V61" s="6"/>
+      <c r="V61" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B62" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
+      <c r="D62" s="5">
+        <v>-105</v>
+      </c>
       <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
+      <c r="F62" s="5">
+        <v>-225</v>
+      </c>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="H62" s="5">
+        <v>-270</v>
+      </c>
       <c r="I62" s="5"/>
-      <c r="J62" s="5"/>
+      <c r="J62" s="5">
+        <v>-180</v>
+      </c>
       <c r="K62" s="5"/>
-      <c r="L62" s="5"/>
+      <c r="L62" s="5">
+        <v>-170</v>
+      </c>
       <c r="M62" s="5"/>
-      <c r="N62" s="5"/>
+      <c r="N62" s="5">
+        <v>-255</v>
+      </c>
       <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
+      <c r="P62" s="5">
+        <v>-235</v>
+      </c>
       <c r="Q62" s="5"/>
-      <c r="R62" s="5"/>
+      <c r="R62" s="5">
+        <v>-270</v>
+      </c>
       <c r="S62" s="5"/>
-      <c r="T62" s="5"/>
+      <c r="T62" s="5">
+        <v>-475</v>
+      </c>
       <c r="U62" s="5"/>
-      <c r="V62" s="6"/>
+      <c r="V62" s="6">
+        <v>-310</v>
+      </c>
     </row>
     <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B64" s="4" t="s">
@@ -3070,83 +3143,83 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B65" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C65" s="5"/>
-      <c r="D65" s="5" t="e">
+      <c r="D65" s="5">
         <f>IF(D62&gt;0,ROUND(ABS(D64)*(D62/100),2),ROUND(D64/(D62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.95</v>
       </c>
       <c r="E65" s="5"/>
-      <c r="F65" s="5" t="e">
+      <c r="F65" s="5">
         <f>IF(F62&gt;0,ROUND(ABS(F64)*(F62/100),2),ROUND(F64/(F62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.44</v>
       </c>
       <c r="G65" s="5"/>
-      <c r="H65" s="5" t="e">
+      <c r="H65" s="5">
         <f>IF(H62&gt;0,ROUND(ABS(H64)*(H62/100),2),ROUND(H64/(H62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.37</v>
       </c>
       <c r="I65" s="5"/>
-      <c r="J65" s="5" t="e">
+      <c r="J65" s="5">
         <f>IF(J62&gt;0,ROUND(ABS(J64)*(J62/100),2),ROUND(J64/(J62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K65" s="5"/>
-      <c r="L65" s="5" t="e">
+      <c r="L65" s="5">
         <f>IF(L62&gt;0,ROUND(ABS(L64)*(L62/100),2),ROUND(L64/(L62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.59</v>
       </c>
       <c r="M65" s="5"/>
-      <c r="N65" s="5" t="e">
+      <c r="N65" s="5">
         <f>IF(N62&gt;0,ROUND(ABS(N64)*(N62/100),2),ROUND(N64/(N62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.39</v>
       </c>
       <c r="O65" s="5"/>
-      <c r="P65" s="5" t="e">
+      <c r="P65" s="5">
         <f>IF(P62&gt;0,ROUND(ABS(P64)*(P62/100),2),ROUND(P64/(P62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.43</v>
       </c>
       <c r="Q65" s="5"/>
-      <c r="R65" s="5" t="e">
+      <c r="R65" s="5">
         <f>IF(R62&gt;0,ROUND(ABS(R64)*(R62/100),2),ROUND(R64/(R62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.37</v>
       </c>
       <c r="S65" s="5"/>
-      <c r="T65" s="5" t="e">
+      <c r="T65" s="5">
         <f>IF(T62&gt;0,ROUND(ABS(T64)*(T62/100),2),ROUND(T64/(T62/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.21</v>
       </c>
       <c r="U65" s="5"/>
-      <c r="V65" s="5" t="e">
+      <c r="V65" s="5">
         <f>IF(V62&gt;0,ROUND(ABS(V64)*(V62/100),2),ROUND(V64/(V62/100),2))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W65" s="8" t="e">
+        <v>0.32</v>
+      </c>
+      <c r="W65" s="8">
         <f>SUM(D65:V65)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="66" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.63</v>
+      </c>
+    </row>
+    <row r="66" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B66" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C66" s="5"/>
       <c r="D66" s="5">
         <f>IF(D61=D59,-D64+D65,0)</f>
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="E66" s="5"/>
       <c r="F66" s="5">
         <f>IF(F61=F59,-F64+F65,0)</f>
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G66" s="5"/>
       <c r="H66" s="5">
         <f>IF(H61=H59,-H64+H65,0)</f>
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="I66" s="5"/>
       <c r="J66" s="5">
@@ -3161,17 +3234,17 @@
       <c r="M66" s="5"/>
       <c r="N66" s="5">
         <f>IF(N61=N59,-N64+N65,0)</f>
-        <v>0</v>
+        <v>1.3900000000000001</v>
       </c>
       <c r="O66" s="5"/>
       <c r="P66" s="5">
         <f>IF(P61=P59,-P64+P65,0)</f>
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Q66" s="5"/>
       <c r="R66" s="5">
         <f>IF(R61=R59,-R64+R65,0)</f>
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S66" s="5"/>
       <c r="T66" s="5">
@@ -3181,31 +3254,423 @@
       <c r="U66" s="5"/>
       <c r="V66" s="6">
         <f>IF(V61=V59,-V64+V65,0)</f>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="W66" s="9">
         <f>SUM(D66:V66)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>10.27</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="W67" s="7">
         <f>W64+W66</f>
+        <v>0.26999999999999957</v>
+      </c>
+    </row>
+    <row r="68" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U68" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="V68" s="13"/>
+      <c r="W68" s="11">
+        <f>W51+W67</f>
+        <v>1.0899999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:23" ht="24" x14ac:dyDescent="0.4">
+      <c r="D69" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="12"/>
+      <c r="H69" s="12"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="12"/>
+      <c r="Q69" s="12"/>
+      <c r="R69" s="12"/>
+      <c r="S69" s="12"/>
+      <c r="T69" s="12"/>
+      <c r="U69" s="12"/>
+      <c r="V69" s="12"/>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D70" t="s">
+        <v>58</v>
+      </c>
+      <c r="F70" t="s">
+        <v>59</v>
+      </c>
+      <c r="H70" t="s">
+        <v>60</v>
+      </c>
+      <c r="J70" t="s">
+        <v>61</v>
+      </c>
+      <c r="L70" t="s">
+        <v>62</v>
+      </c>
+      <c r="N70" t="s">
+        <v>63</v>
+      </c>
+      <c r="P70" t="s">
+        <v>64</v>
+      </c>
+      <c r="R70" t="s">
+        <v>65</v>
+      </c>
+      <c r="T70" t="s">
+        <v>66</v>
+      </c>
+      <c r="V70" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A71">
+        <v>3.5</v>
+      </c>
+      <c r="B71" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>2.5</v>
+      </c>
+      <c r="B72" s="1">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A73">
+        <v>3.5</v>
+      </c>
+      <c r="B73" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A74">
+        <v>2.5</v>
+      </c>
+      <c r="B74" s="1">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B76" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5"/>
+      <c r="K76" s="5"/>
+      <c r="L76" s="5"/>
+      <c r="M76" s="5"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="5"/>
+      <c r="P76" s="5"/>
+      <c r="Q76" s="5"/>
+      <c r="R76" s="5"/>
+      <c r="S76" s="5"/>
+      <c r="T76" s="5"/>
+      <c r="U76" s="5"/>
+      <c r="V76" s="6"/>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B77" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C77" s="5"/>
+      <c r="D77" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="G77" s="5"/>
+      <c r="H77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="I77" s="5"/>
+      <c r="J77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="K77" s="5"/>
+      <c r="L77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="M77" s="5"/>
+      <c r="N77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="O77" s="5"/>
+      <c r="P77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="Q77" s="5"/>
+      <c r="R77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="S77" s="5"/>
+      <c r="T77" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="U77" s="5"/>
+      <c r="V77" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B78" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+      <c r="I78" s="5"/>
+      <c r="J78" s="5"/>
+      <c r="K78" s="5"/>
+      <c r="L78" s="5"/>
+      <c r="M78" s="5"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="5"/>
+      <c r="P78" s="5"/>
+      <c r="Q78" s="5"/>
+      <c r="R78" s="5"/>
+      <c r="S78" s="5"/>
+      <c r="T78" s="5"/>
+      <c r="U78" s="5"/>
+      <c r="V78" s="6"/>
+    </row>
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B79" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+      <c r="I79" s="5"/>
+      <c r="J79" s="5"/>
+      <c r="K79" s="5"/>
+      <c r="L79" s="5"/>
+      <c r="M79" s="5"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="5"/>
+      <c r="P79" s="5"/>
+      <c r="Q79" s="5"/>
+      <c r="R79" s="5"/>
+      <c r="S79" s="5"/>
+      <c r="T79" s="5"/>
+      <c r="U79" s="5"/>
+      <c r="V79" s="6"/>
+    </row>
+    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B81" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C81" s="5"/>
+      <c r="D81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G81" s="5"/>
+      <c r="H81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I81" s="5"/>
+      <c r="J81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="K81" s="5"/>
+      <c r="L81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="M81" s="5"/>
+      <c r="N81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="O81" s="5"/>
+      <c r="P81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q81" s="5"/>
+      <c r="R81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S81" s="5"/>
+      <c r="T81" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U81" s="5"/>
+      <c r="V81" s="6">
+        <v>-1</v>
+      </c>
+      <c r="W81" s="8">
+        <f>SUM(D81:V81)</f>
         <v>-10</v>
       </c>
     </row>
-    <row r="68" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U68" s="12" t="s">
+    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B82" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C82" s="5"/>
+      <c r="D82" s="5" t="e">
+        <f>IF(D79&gt;0,ROUND(ABS(D81)*(D79/100),2),ROUND(D81/(D79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5" t="e">
+        <f>IF(F79&gt;0,ROUND(ABS(F81)*(F79/100),2),ROUND(F81/(F79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G82" s="5"/>
+      <c r="H82" s="5" t="e">
+        <f>IF(H79&gt;0,ROUND(ABS(H81)*(H79/100),2),ROUND(H81/(H79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I82" s="5"/>
+      <c r="J82" s="5" t="e">
+        <f>IF(J79&gt;0,ROUND(ABS(J81)*(J79/100),2),ROUND(J81/(J79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K82" s="5"/>
+      <c r="L82" s="5" t="e">
+        <f>IF(L79&gt;0,ROUND(ABS(L81)*(L79/100),2),ROUND(L81/(L79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M82" s="5"/>
+      <c r="N82" s="5" t="e">
+        <f>IF(N79&gt;0,ROUND(ABS(N81)*(N79/100),2),ROUND(N81/(N79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O82" s="5"/>
+      <c r="P82" s="5" t="e">
+        <f>IF(P79&gt;0,ROUND(ABS(P81)*(P79/100),2),ROUND(P81/(P79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q82" s="5"/>
+      <c r="R82" s="5" t="e">
+        <f>IF(R79&gt;0,ROUND(ABS(R81)*(R79/100),2),ROUND(R81/(R79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S82" s="5"/>
+      <c r="T82" s="5" t="e">
+        <f>IF(T79&gt;0,ROUND(ABS(T81)*(T79/100),2),ROUND(T81/(T79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U82" s="5"/>
+      <c r="V82" s="5" t="e">
+        <f>IF(V79&gt;0,ROUND(ABS(V81)*(V79/100),2),ROUND(V81/(V79/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W82" s="8" t="e">
+        <f>SUM(D82:V82)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="83" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B83" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C83" s="5"/>
+      <c r="D83" s="5" t="e">
+        <f>IF(D78=D76,-D81+D82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5" t="e">
+        <f>IF(F78=F76,-F81+F82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G83" s="5"/>
+      <c r="H83" s="5" t="e">
+        <f>IF(H78=H76,-H81+H82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5" t="e">
+        <f>IF(J78=J76,-J81+J82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K83" s="5"/>
+      <c r="L83" s="5" t="e">
+        <f>IF(L78=L76,-L81+L82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="M83" s="5"/>
+      <c r="N83" s="5" t="e">
+        <f>IF(N78=N76,-N81+N82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O83" s="5"/>
+      <c r="P83" s="5" t="e">
+        <f>IF(P78=P76,-P81+P82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q83" s="5"/>
+      <c r="R83" s="5" t="e">
+        <f>IF(R78=R76,-R81+R82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="S83" s="5"/>
+      <c r="T83" s="5" t="e">
+        <f>IF(T78=T76,-T81+T82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U83" s="5"/>
+      <c r="V83" s="6" t="e">
+        <f>IF(V78=V76,-V81+V82,0)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W83" s="9" t="e">
+        <f>SUM(D83:V83)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="84" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W84" s="7" t="e">
+        <f>W81+W83</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="85" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U85" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V68" s="12"/>
-      <c r="W68" s="11" t="e">
-        <f>#REF!+W67</f>
-        <v>#REF!</v>
+      <c r="V85" s="13"/>
+      <c r="W85" s="11" t="e">
+        <f>W68+W84</f>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
+    <mergeCell ref="D69:V69"/>
+    <mergeCell ref="U85:V85"/>
     <mergeCell ref="D52:V52"/>
     <mergeCell ref="U68:V68"/>
     <mergeCell ref="U51:V51"/>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git-Folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FACF32F3-9BBB-4C84-8EF9-6C5B62D3904E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD46430-99A3-4ED9-AFBA-36FD89D25E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions 2(Records)" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="69">
   <si>
     <t>Goals</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>SUN vs EVE</t>
+  </si>
+  <si>
+    <t>Match Week 11</t>
   </si>
 </sst>
 </file>
@@ -1245,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA341253-1EAB-4104-BE4B-374BC158237A}">
-  <dimension ref="A1:W85"/>
+  <dimension ref="A1:W102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:23" ht="24" x14ac:dyDescent="0.4">
@@ -3339,6 +3342,36 @@
       <c r="B71" s="1">
         <v>0.8</v>
       </c>
+      <c r="D71" t="s">
+        <v>13</v>
+      </c>
+      <c r="F71" t="s">
+        <v>13</v>
+      </c>
+      <c r="H71" t="s">
+        <v>14</v>
+      </c>
+      <c r="J71" t="s">
+        <v>13</v>
+      </c>
+      <c r="L71" t="s">
+        <v>13</v>
+      </c>
+      <c r="N71" t="s">
+        <v>13</v>
+      </c>
+      <c r="P71" t="s">
+        <v>13</v>
+      </c>
+      <c r="R71" t="s">
+        <v>13</v>
+      </c>
+      <c r="T71" t="s">
+        <v>13</v>
+      </c>
+      <c r="V71" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72">
@@ -3347,6 +3380,36 @@
       <c r="B72" s="1">
         <v>0.8</v>
       </c>
+      <c r="D72" t="s">
+        <v>13</v>
+      </c>
+      <c r="F72" t="s">
+        <v>13</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" t="s">
+        <v>13</v>
+      </c>
+      <c r="L72" t="s">
+        <v>13</v>
+      </c>
+      <c r="N72" t="s">
+        <v>13</v>
+      </c>
+      <c r="P72" t="s">
+        <v>13</v>
+      </c>
+      <c r="R72" t="s">
+        <v>13</v>
+      </c>
+      <c r="T72" t="s">
+        <v>13</v>
+      </c>
+      <c r="V72" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73">
@@ -3354,6 +3417,36 @@
       </c>
       <c r="B73" s="1">
         <v>0.7</v>
+      </c>
+      <c r="D73" t="s">
+        <v>13</v>
+      </c>
+      <c r="F73" t="s">
+        <v>13</v>
+      </c>
+      <c r="H73" t="s">
+        <v>14</v>
+      </c>
+      <c r="J73" t="s">
+        <v>13</v>
+      </c>
+      <c r="L73" t="s">
+        <v>13</v>
+      </c>
+      <c r="N73" t="s">
+        <v>13</v>
+      </c>
+      <c r="P73" t="s">
+        <v>13</v>
+      </c>
+      <c r="R73" t="s">
+        <v>13</v>
+      </c>
+      <c r="T73" t="s">
+        <v>13</v>
+      </c>
+      <c r="V73" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:23" x14ac:dyDescent="0.25">
@@ -3363,31 +3456,81 @@
       <c r="B74" s="1">
         <v>0.7</v>
       </c>
+      <c r="D74" t="s">
+        <v>13</v>
+      </c>
+      <c r="F74" t="s">
+        <v>13</v>
+      </c>
+      <c r="H74" t="s">
+        <v>14</v>
+      </c>
+      <c r="J74" t="s">
+        <v>13</v>
+      </c>
+      <c r="L74" t="s">
+        <v>13</v>
+      </c>
+      <c r="N74" t="s">
+        <v>13</v>
+      </c>
+      <c r="P74" t="s">
+        <v>13</v>
+      </c>
+      <c r="R74" t="s">
+        <v>13</v>
+      </c>
+      <c r="T74" t="s">
+        <v>13</v>
+      </c>
+      <c r="V74" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B76" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="5"/>
-      <c r="D76" s="5"/>
+      <c r="D76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E76" s="5"/>
-      <c r="F76" s="5"/>
+      <c r="F76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="I76" s="5"/>
-      <c r="J76" s="5"/>
+      <c r="J76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K76" s="5"/>
-      <c r="L76" s="5"/>
+      <c r="L76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="M76" s="5"/>
-      <c r="N76" s="5"/>
+      <c r="N76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
+      <c r="P76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="Q76" s="5"/>
-      <c r="R76" s="5"/>
+      <c r="R76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="S76" s="5"/>
-      <c r="T76" s="5"/>
+      <c r="T76" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="U76" s="5"/>
-      <c r="V76" s="6"/>
+      <c r="V76" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B77" s="4" t="s">
@@ -3395,7 +3538,7 @@
       </c>
       <c r="C77" s="5"/>
       <c r="D77" s="5">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="E77" s="5"/>
       <c r="F77" s="5">
@@ -3403,7 +3546,7 @@
       </c>
       <c r="G77" s="5"/>
       <c r="H77" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="I77" s="5"/>
       <c r="J77" s="5">
@@ -3439,52 +3582,92 @@
         <v>16</v>
       </c>
       <c r="C78" s="5"/>
-      <c r="D78" s="5"/>
+      <c r="D78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="E78" s="5"/>
-      <c r="F78" s="5"/>
+      <c r="F78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="I78" s="5"/>
-      <c r="J78" s="5"/>
+      <c r="J78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="K78" s="5"/>
-      <c r="L78" s="5"/>
+      <c r="L78" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="M78" s="5"/>
-      <c r="N78" s="5"/>
+      <c r="N78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="O78" s="5"/>
-      <c r="P78" s="5"/>
+      <c r="P78" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="Q78" s="5"/>
-      <c r="R78" s="5"/>
+      <c r="R78" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="S78" s="5"/>
-      <c r="T78" s="5"/>
+      <c r="T78" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="U78" s="5"/>
-      <c r="V78" s="6"/>
+      <c r="V78" s="6" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B79" s="4" t="s">
         <v>17</v>
       </c>
       <c r="C79" s="5"/>
-      <c r="D79" s="5"/>
+      <c r="D79" s="5">
+        <v>-290</v>
+      </c>
       <c r="E79" s="5"/>
-      <c r="F79" s="5"/>
+      <c r="F79" s="5">
+        <v>-275</v>
+      </c>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
+      <c r="H79" s="5">
+        <v>-105</v>
+      </c>
       <c r="I79" s="5"/>
-      <c r="J79" s="5"/>
+      <c r="J79" s="5">
+        <v>-280</v>
+      </c>
       <c r="K79" s="5"/>
-      <c r="L79" s="5"/>
+      <c r="L79" s="5">
+        <v>-235</v>
+      </c>
       <c r="M79" s="5"/>
-      <c r="N79" s="5"/>
+      <c r="N79" s="5">
+        <v>-265</v>
+      </c>
       <c r="O79" s="5"/>
-      <c r="P79" s="5"/>
+      <c r="P79" s="5">
+        <v>-160</v>
+      </c>
       <c r="Q79" s="5"/>
-      <c r="R79" s="5"/>
+      <c r="R79" s="5">
+        <v>-260</v>
+      </c>
       <c r="S79" s="5"/>
-      <c r="T79" s="5"/>
+      <c r="T79" s="5">
+        <v>-175</v>
+      </c>
       <c r="U79" s="5"/>
-      <c r="V79" s="6"/>
-    </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="V79" s="6">
+        <v>-475</v>
+      </c>
+    </row>
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B81" s="4" t="s">
         <v>18</v>
       </c>
@@ -3533,142 +3716,714 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B82" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C82" s="5"/>
-      <c r="D82" s="5" t="e">
+      <c r="D82" s="5">
         <f>IF(D79&gt;0,ROUND(ABS(D81)*(D79/100),2),ROUND(D81/(D79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.34</v>
       </c>
       <c r="E82" s="5"/>
-      <c r="F82" s="5" t="e">
+      <c r="F82" s="5">
         <f>IF(F79&gt;0,ROUND(ABS(F81)*(F79/100),2),ROUND(F81/(F79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.36</v>
       </c>
       <c r="G82" s="5"/>
-      <c r="H82" s="5" t="e">
+      <c r="H82" s="5">
         <f>IF(H79&gt;0,ROUND(ABS(H81)*(H79/100),2),ROUND(H81/(H79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.95</v>
       </c>
       <c r="I82" s="5"/>
-      <c r="J82" s="5" t="e">
+      <c r="J82" s="5">
         <f>IF(J79&gt;0,ROUND(ABS(J81)*(J79/100),2),ROUND(J81/(J79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.36</v>
       </c>
       <c r="K82" s="5"/>
-      <c r="L82" s="5" t="e">
+      <c r="L82" s="5">
         <f>IF(L79&gt;0,ROUND(ABS(L81)*(L79/100),2),ROUND(L81/(L79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.43</v>
       </c>
       <c r="M82" s="5"/>
-      <c r="N82" s="5" t="e">
+      <c r="N82" s="5">
         <f>IF(N79&gt;0,ROUND(ABS(N81)*(N79/100),2),ROUND(N81/(N79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.38</v>
       </c>
       <c r="O82" s="5"/>
-      <c r="P82" s="5" t="e">
+      <c r="P82" s="5">
         <f>IF(P79&gt;0,ROUND(ABS(P81)*(P79/100),2),ROUND(P81/(P79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.63</v>
       </c>
       <c r="Q82" s="5"/>
-      <c r="R82" s="5" t="e">
+      <c r="R82" s="5">
         <f>IF(R79&gt;0,ROUND(ABS(R81)*(R79/100),2),ROUND(R81/(R79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.38</v>
       </c>
       <c r="S82" s="5"/>
-      <c r="T82" s="5" t="e">
+      <c r="T82" s="5">
         <f>IF(T79&gt;0,ROUND(ABS(T81)*(T79/100),2),ROUND(T81/(T79/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="U82" s="5"/>
-      <c r="V82" s="5" t="e">
+      <c r="V82" s="5">
         <f>IF(V79&gt;0,ROUND(ABS(V81)*(V79/100),2),ROUND(V81/(V79/100),2))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W82" s="8" t="e">
+        <v>0.21</v>
+      </c>
+      <c r="W82" s="8">
         <f>SUM(D82:V82)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="83" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>4.6099999999999994</v>
+      </c>
+    </row>
+    <row r="83" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
         <v>20</v>
       </c>
       <c r="C83" s="5"/>
-      <c r="D83" s="5" t="e">
+      <c r="D83" s="5">
         <f>IF(D78=D76,-D81+D82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.34</v>
       </c>
       <c r="E83" s="5"/>
-      <c r="F83" s="5" t="e">
+      <c r="F83" s="5">
         <f>IF(F78=F76,-F81+F82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="G83" s="5"/>
-      <c r="H83" s="5" t="e">
+      <c r="H83" s="5">
         <f>IF(H78=H76,-H81+H82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.95</v>
       </c>
       <c r="I83" s="5"/>
-      <c r="J83" s="5" t="e">
+      <c r="J83" s="5">
         <f>IF(J78=J76,-J81+J82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.3599999999999999</v>
       </c>
       <c r="K83" s="5"/>
-      <c r="L83" s="5" t="e">
+      <c r="L83" s="5">
         <f>IF(L78=L76,-L81+L82,0)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="M83" s="5"/>
-      <c r="N83" s="5" t="e">
+      <c r="N83" s="5">
         <f>IF(N78=N76,-N81+N82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.38</v>
       </c>
       <c r="O83" s="5"/>
-      <c r="P83" s="5" t="e">
+      <c r="P83" s="5">
         <f>IF(P78=P76,-P81+P82,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.63</v>
       </c>
       <c r="Q83" s="5"/>
-      <c r="R83" s="5" t="e">
+      <c r="R83" s="5">
         <f>IF(R78=R76,-R81+R82,0)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="S83" s="5"/>
-      <c r="T83" s="5" t="e">
+      <c r="T83" s="5">
         <f>IF(T78=T76,-T81+T82,0)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="U83" s="5"/>
-      <c r="V83" s="6" t="e">
+      <c r="V83" s="6">
         <f>IF(V78=V76,-V81+V82,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W83" s="9" t="e">
+        <v>1.21</v>
+      </c>
+      <c r="W83" s="9">
         <f>SUM(D83:V83)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="84" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="W84" s="7" t="e">
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W84" s="7">
         <f>W81+W83</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="85" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.23000000000000043</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="U85" s="13" t="s">
         <v>44</v>
       </c>
       <c r="V85" s="13"/>
-      <c r="W85" s="11" t="e">
+      <c r="W85" s="11">
         <f>W68+W84</f>
-        <v>#DIV/0!</v>
+        <v>1.3200000000000003</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" ht="24" x14ac:dyDescent="0.4">
+      <c r="D86" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="12"/>
+      <c r="H86" s="12"/>
+      <c r="I86" s="12"/>
+      <c r="J86" s="12"/>
+      <c r="K86" s="12"/>
+      <c r="L86" s="12"/>
+      <c r="M86" s="12"/>
+      <c r="N86" s="12"/>
+      <c r="O86" s="12"/>
+      <c r="P86" s="12"/>
+      <c r="Q86" s="12"/>
+      <c r="R86" s="12"/>
+      <c r="S86" s="12"/>
+      <c r="T86" s="12"/>
+      <c r="U86" s="12"/>
+      <c r="V86" s="12"/>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="D87" t="s">
+        <v>58</v>
+      </c>
+      <c r="F87" t="s">
+        <v>59</v>
+      </c>
+      <c r="H87" t="s">
+        <v>60</v>
+      </c>
+      <c r="J87" t="s">
+        <v>61</v>
+      </c>
+      <c r="L87" t="s">
+        <v>62</v>
+      </c>
+      <c r="N87" t="s">
+        <v>63</v>
+      </c>
+      <c r="P87" t="s">
+        <v>64</v>
+      </c>
+      <c r="R87" t="s">
+        <v>65</v>
+      </c>
+      <c r="T87" t="s">
+        <v>66</v>
+      </c>
+      <c r="V87" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A88">
+        <v>3.5</v>
+      </c>
+      <c r="B88" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D88" t="s">
+        <v>13</v>
+      </c>
+      <c r="F88" t="s">
+        <v>13</v>
+      </c>
+      <c r="H88" t="s">
+        <v>14</v>
+      </c>
+      <c r="J88" t="s">
+        <v>13</v>
+      </c>
+      <c r="L88" t="s">
+        <v>13</v>
+      </c>
+      <c r="N88" t="s">
+        <v>13</v>
+      </c>
+      <c r="P88" t="s">
+        <v>13</v>
+      </c>
+      <c r="R88" t="s">
+        <v>13</v>
+      </c>
+      <c r="T88" t="s">
+        <v>13</v>
+      </c>
+      <c r="V88" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A89">
+        <v>2.5</v>
+      </c>
+      <c r="B89" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="D89" t="s">
+        <v>13</v>
+      </c>
+      <c r="F89" t="s">
+        <v>13</v>
+      </c>
+      <c r="H89" t="s">
+        <v>14</v>
+      </c>
+      <c r="J89" t="s">
+        <v>13</v>
+      </c>
+      <c r="L89" t="s">
+        <v>13</v>
+      </c>
+      <c r="N89" t="s">
+        <v>13</v>
+      </c>
+      <c r="P89" t="s">
+        <v>13</v>
+      </c>
+      <c r="R89" t="s">
+        <v>13</v>
+      </c>
+      <c r="T89" t="s">
+        <v>13</v>
+      </c>
+      <c r="V89" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A90">
+        <v>3.5</v>
+      </c>
+      <c r="B90" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="F90" t="s">
+        <v>13</v>
+      </c>
+      <c r="H90" t="s">
+        <v>14</v>
+      </c>
+      <c r="J90" t="s">
+        <v>13</v>
+      </c>
+      <c r="L90" t="s">
+        <v>13</v>
+      </c>
+      <c r="N90" t="s">
+        <v>13</v>
+      </c>
+      <c r="P90" t="s">
+        <v>13</v>
+      </c>
+      <c r="R90" t="s">
+        <v>13</v>
+      </c>
+      <c r="T90" t="s">
+        <v>13</v>
+      </c>
+      <c r="V90" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A91">
+        <v>2.5</v>
+      </c>
+      <c r="B91" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="F91" t="s">
+        <v>13</v>
+      </c>
+      <c r="H91" t="s">
+        <v>14</v>
+      </c>
+      <c r="J91" t="s">
+        <v>13</v>
+      </c>
+      <c r="L91" t="s">
+        <v>13</v>
+      </c>
+      <c r="N91" t="s">
+        <v>13</v>
+      </c>
+      <c r="P91" t="s">
+        <v>13</v>
+      </c>
+      <c r="R91" t="s">
+        <v>13</v>
+      </c>
+      <c r="T91" t="s">
+        <v>13</v>
+      </c>
+      <c r="V91" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B93" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="5"/>
+      <c r="D93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G93" s="5"/>
+      <c r="H93" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K93" s="5"/>
+      <c r="L93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="M93" s="5"/>
+      <c r="N93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O93" s="5"/>
+      <c r="P93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q93" s="5"/>
+      <c r="R93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="S93" s="5"/>
+      <c r="T93" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="U93" s="5"/>
+      <c r="V93" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B94" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="5"/>
+      <c r="D94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="G94" s="5"/>
+      <c r="H94" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="I94" s="5"/>
+      <c r="J94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="K94" s="5"/>
+      <c r="L94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="M94" s="5"/>
+      <c r="N94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="O94" s="5"/>
+      <c r="P94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="Q94" s="5"/>
+      <c r="R94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="S94" s="5"/>
+      <c r="T94" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="U94" s="5"/>
+      <c r="V94" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B95" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" s="5"/>
+      <c r="D95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="G95" s="5"/>
+      <c r="H95" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="I95" s="5"/>
+      <c r="J95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="K95" s="5"/>
+      <c r="L95" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="M95" s="5"/>
+      <c r="N95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="O95" s="5"/>
+      <c r="P95" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q95" s="5"/>
+      <c r="R95" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="S95" s="5"/>
+      <c r="T95" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="U95" s="5"/>
+      <c r="V95" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B96" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C96" s="5"/>
+      <c r="D96" s="5">
+        <v>-290</v>
+      </c>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5">
+        <v>-275</v>
+      </c>
+      <c r="G96" s="5"/>
+      <c r="H96" s="5">
+        <v>-105</v>
+      </c>
+      <c r="I96" s="5"/>
+      <c r="J96" s="5">
+        <v>-280</v>
+      </c>
+      <c r="K96" s="5"/>
+      <c r="L96" s="5">
+        <v>-235</v>
+      </c>
+      <c r="M96" s="5"/>
+      <c r="N96" s="5">
+        <v>-265</v>
+      </c>
+      <c r="O96" s="5"/>
+      <c r="P96" s="5">
+        <v>-160</v>
+      </c>
+      <c r="Q96" s="5"/>
+      <c r="R96" s="5">
+        <v>-260</v>
+      </c>
+      <c r="S96" s="5"/>
+      <c r="T96" s="5">
+        <v>-175</v>
+      </c>
+      <c r="U96" s="5"/>
+      <c r="V96" s="6">
+        <v>-475</v>
+      </c>
+    </row>
+    <row r="98" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B98" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C98" s="5"/>
+      <c r="D98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="G98" s="5"/>
+      <c r="H98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="I98" s="5"/>
+      <c r="J98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="M98" s="5"/>
+      <c r="N98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="O98" s="5"/>
+      <c r="P98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="Q98" s="5"/>
+      <c r="R98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="S98" s="5"/>
+      <c r="T98" s="5">
+        <v>-1</v>
+      </c>
+      <c r="U98" s="5"/>
+      <c r="V98" s="6">
+        <v>-1</v>
+      </c>
+      <c r="W98" s="8">
+        <f>SUM(D98:V98)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="99" spans="2:23" x14ac:dyDescent="0.25">
+      <c r="B99" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" s="5"/>
+      <c r="D99" s="5">
+        <f>IF(D96&gt;0,ROUND(ABS(D98)*(D96/100),2),ROUND(D98/(D96/100),2))</f>
+        <v>0.34</v>
+      </c>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5">
+        <f>IF(F96&gt;0,ROUND(ABS(F98)*(F96/100),2),ROUND(F98/(F96/100),2))</f>
+        <v>0.36</v>
+      </c>
+      <c r="G99" s="5"/>
+      <c r="H99" s="5">
+        <f>IF(H96&gt;0,ROUND(ABS(H98)*(H96/100),2),ROUND(H98/(H96/100),2))</f>
+        <v>0.95</v>
+      </c>
+      <c r="I99" s="5"/>
+      <c r="J99" s="5">
+        <f>IF(J96&gt;0,ROUND(ABS(J98)*(J96/100),2),ROUND(J98/(J96/100),2))</f>
+        <v>0.36</v>
+      </c>
+      <c r="K99" s="5"/>
+      <c r="L99" s="5">
+        <f>IF(L96&gt;0,ROUND(ABS(L98)*(L96/100),2),ROUND(L98/(L96/100),2))</f>
+        <v>0.43</v>
+      </c>
+      <c r="M99" s="5"/>
+      <c r="N99" s="5">
+        <f>IF(N96&gt;0,ROUND(ABS(N98)*(N96/100),2),ROUND(N98/(N96/100),2))</f>
+        <v>0.38</v>
+      </c>
+      <c r="O99" s="5"/>
+      <c r="P99" s="5">
+        <f>IF(P96&gt;0,ROUND(ABS(P98)*(P96/100),2),ROUND(P98/(P96/100),2))</f>
+        <v>0.63</v>
+      </c>
+      <c r="Q99" s="5"/>
+      <c r="R99" s="5">
+        <f>IF(R96&gt;0,ROUND(ABS(R98)*(R96/100),2),ROUND(R98/(R96/100),2))</f>
+        <v>0.38</v>
+      </c>
+      <c r="S99" s="5"/>
+      <c r="T99" s="5">
+        <f>IF(T96&gt;0,ROUND(ABS(T98)*(T96/100),2),ROUND(T98/(T96/100),2))</f>
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="U99" s="5"/>
+      <c r="V99" s="5">
+        <f>IF(V96&gt;0,ROUND(ABS(V98)*(V96/100),2),ROUND(V98/(V96/100),2))</f>
+        <v>0.21</v>
+      </c>
+      <c r="W99" s="8">
+        <f>SUM(D99:V99)</f>
+        <v>4.6099999999999994</v>
+      </c>
+    </row>
+    <row r="100" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B100" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C100" s="5"/>
+      <c r="D100" s="5">
+        <f>IF(D95=D93,-D98+D99,0)</f>
+        <v>1.34</v>
+      </c>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5">
+        <f>IF(F95=F93,-F98+F99,0)</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="G100" s="5"/>
+      <c r="H100" s="5">
+        <f>IF(H95=H93,-H98+H99,0)</f>
+        <v>1.95</v>
+      </c>
+      <c r="I100" s="5"/>
+      <c r="J100" s="5">
+        <f>IF(J95=J93,-J98+J99,0)</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="K100" s="5"/>
+      <c r="L100" s="5">
+        <f>IF(L95=L93,-L98+L99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M100" s="5"/>
+      <c r="N100" s="5">
+        <f>IF(N95=N93,-N98+N99,0)</f>
+        <v>1.38</v>
+      </c>
+      <c r="O100" s="5"/>
+      <c r="P100" s="5">
+        <f>IF(P95=P93,-P98+P99,0)</f>
+        <v>1.63</v>
+      </c>
+      <c r="Q100" s="5"/>
+      <c r="R100" s="5">
+        <f>IF(R95=R93,-R98+R99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S100" s="5"/>
+      <c r="T100" s="5">
+        <f>IF(T95=T93,-T98+T99,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U100" s="5"/>
+      <c r="V100" s="6">
+        <f>IF(V95=V93,-V98+V99,0)</f>
+        <v>1.21</v>
+      </c>
+      <c r="W100" s="9">
+        <f>SUM(D100:V100)</f>
+        <v>10.23</v>
+      </c>
+    </row>
+    <row r="101" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W101" s="7">
+        <f>W98+W100</f>
+        <v>0.23000000000000043</v>
+      </c>
+    </row>
+    <row r="102" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="U102" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="V102" s="13"/>
+      <c r="W102" s="11">
+        <f>W85+W101</f>
+        <v>1.5500000000000007</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="12">
+    <mergeCell ref="D86:V86"/>
+    <mergeCell ref="U102:V102"/>
     <mergeCell ref="D69:V69"/>
     <mergeCell ref="U85:V85"/>
     <mergeCell ref="D52:V52"/>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git-Folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD46430-99A3-4ED9-AFBA-36FD89D25E1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB6499A-1643-4216-84F4-12E37C95FA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="79">
   <si>
     <t>Goals</t>
   </si>
@@ -240,6 +240,36 @@
   </si>
   <si>
     <t>Match Week 11</t>
+  </si>
+  <si>
+    <t>TOT vs MUN</t>
+  </si>
+  <si>
+    <t>EVE vs FUL</t>
+  </si>
+  <si>
+    <t>WHU vs BUR</t>
+  </si>
+  <si>
+    <t>SUN vs ARS</t>
+  </si>
+  <si>
+    <t>CHE vs WOL</t>
+  </si>
+  <si>
+    <t>BRE vs NCU</t>
+  </si>
+  <si>
+    <t>AVL vs BOU</t>
+  </si>
+  <si>
+    <t>CRY vs BHA</t>
+  </si>
+  <si>
+    <t>NOF vs LEE</t>
+  </si>
+  <si>
+    <t>MCI vs LIV</t>
   </si>
 </sst>
 </file>
@@ -3875,34 +3905,34 @@
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="F87" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="H87" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="J87" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="L87" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="N87" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="P87" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="R87" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="T87" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="V87" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" spans="1:23" x14ac:dyDescent="0.25">
@@ -3916,10 +3946,10 @@
         <v>13</v>
       </c>
       <c r="F88" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H88" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J88" t="s">
         <v>13</v>
@@ -3931,7 +3961,7 @@
         <v>13</v>
       </c>
       <c r="P88" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R88" t="s">
         <v>13</v>
@@ -3954,10 +3984,10 @@
         <v>13</v>
       </c>
       <c r="F89" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H89" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J89" t="s">
         <v>13</v>
@@ -3969,7 +3999,7 @@
         <v>13</v>
       </c>
       <c r="P89" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R89" t="s">
         <v>13</v>
@@ -3992,10 +4022,10 @@
         <v>13</v>
       </c>
       <c r="F90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H90" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J90" t="s">
         <v>13</v>
@@ -4007,7 +4037,7 @@
         <v>13</v>
       </c>
       <c r="P90" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R90" t="s">
         <v>13</v>
@@ -4030,10 +4060,10 @@
         <v>13</v>
       </c>
       <c r="F91" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H91" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J91" t="s">
         <v>13</v>
@@ -4045,7 +4075,7 @@
         <v>13</v>
       </c>
       <c r="P91" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R91" t="s">
         <v>13</v>
@@ -4067,11 +4097,11 @@
       </c>
       <c r="E93" s="5"/>
       <c r="F93" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G93" s="5"/>
       <c r="H93" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I93" s="5"/>
       <c r="J93" s="5" t="s">
@@ -4087,7 +4117,7 @@
       </c>
       <c r="O93" s="5"/>
       <c r="P93" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="Q93" s="5"/>
       <c r="R93" s="5" t="s">
@@ -4112,11 +4142,11 @@
       </c>
       <c r="E94" s="5"/>
       <c r="F94" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="G94" s="5"/>
       <c r="H94" s="5">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="I94" s="5"/>
       <c r="J94" s="5">
@@ -4152,45 +4182,25 @@
         <v>16</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="D95" s="5"/>
       <c r="E95" s="5"/>
-      <c r="F95" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="F95" s="5"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="H95" s="5"/>
       <c r="I95" s="5"/>
-      <c r="J95" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="J95" s="5"/>
       <c r="K95" s="5"/>
-      <c r="L95" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="L95" s="5"/>
       <c r="M95" s="5"/>
-      <c r="N95" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="N95" s="5"/>
       <c r="O95" s="5"/>
-      <c r="P95" s="5" t="s">
-        <v>13</v>
-      </c>
+      <c r="P95" s="5"/>
       <c r="Q95" s="5"/>
-      <c r="R95" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="R95" s="5"/>
       <c r="S95" s="5"/>
-      <c r="T95" s="5" t="s">
-        <v>14</v>
-      </c>
+      <c r="T95" s="5"/>
       <c r="U95" s="5"/>
-      <c r="V95" s="6" t="s">
-        <v>13</v>
-      </c>
+      <c r="V95" s="6"/>
     </row>
     <row r="96" spans="1:23" x14ac:dyDescent="0.25">
       <c r="B96" s="4" t="s">
@@ -4198,43 +4208,43 @@
       </c>
       <c r="C96" s="5"/>
       <c r="D96" s="5">
-        <v>-290</v>
+        <v>-190</v>
       </c>
       <c r="E96" s="5"/>
       <c r="F96" s="5">
-        <v>-275</v>
+        <v>115</v>
       </c>
       <c r="G96" s="5"/>
       <c r="H96" s="5">
-        <v>-105</v>
+        <v>-350</v>
       </c>
       <c r="I96" s="5"/>
       <c r="J96" s="5">
-        <v>-280</v>
+        <v>-380</v>
       </c>
       <c r="K96" s="5"/>
       <c r="L96" s="5">
-        <v>-235</v>
+        <v>-210</v>
       </c>
       <c r="M96" s="5"/>
       <c r="N96" s="5">
-        <v>-265</v>
+        <v>-230</v>
       </c>
       <c r="O96" s="5"/>
       <c r="P96" s="5">
-        <v>-160</v>
+        <v>-120</v>
       </c>
       <c r="Q96" s="5"/>
       <c r="R96" s="5">
-        <v>-260</v>
+        <v>-270</v>
       </c>
       <c r="S96" s="5"/>
       <c r="T96" s="5">
-        <v>-175</v>
+        <v>-350</v>
       </c>
       <c r="U96" s="5"/>
       <c r="V96" s="6">
-        <v>-475</v>
+        <v>-145</v>
       </c>
     </row>
     <row r="98" spans="2:23" x14ac:dyDescent="0.25">
@@ -4293,56 +4303,56 @@
       <c r="C99" s="5"/>
       <c r="D99" s="5">
         <f>IF(D96&gt;0,ROUND(ABS(D98)*(D96/100),2),ROUND(D98/(D96/100),2))</f>
-        <v>0.34</v>
+        <v>0.53</v>
       </c>
       <c r="E99" s="5"/>
       <c r="F99" s="5">
         <f>IF(F96&gt;0,ROUND(ABS(F98)*(F96/100),2),ROUND(F98/(F96/100),2))</f>
-        <v>0.36</v>
+        <v>1.1499999999999999</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="5">
         <f>IF(H96&gt;0,ROUND(ABS(H98)*(H96/100),2),ROUND(H98/(H96/100),2))</f>
-        <v>0.95</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="I99" s="5"/>
       <c r="J99" s="5">
         <f>IF(J96&gt;0,ROUND(ABS(J98)*(J96/100),2),ROUND(J98/(J96/100),2))</f>
-        <v>0.36</v>
+        <v>0.26</v>
       </c>
       <c r="K99" s="5"/>
       <c r="L99" s="5">
         <f>IF(L96&gt;0,ROUND(ABS(L98)*(L96/100),2),ROUND(L98/(L96/100),2))</f>
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="M99" s="5"/>
       <c r="N99" s="5">
         <f>IF(N96&gt;0,ROUND(ABS(N98)*(N96/100),2),ROUND(N98/(N96/100),2))</f>
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="O99" s="5"/>
       <c r="P99" s="5">
         <f>IF(P96&gt;0,ROUND(ABS(P98)*(P96/100),2),ROUND(P98/(P96/100),2))</f>
-        <v>0.63</v>
+        <v>0.83</v>
       </c>
       <c r="Q99" s="5"/>
       <c r="R99" s="5">
         <f>IF(R96&gt;0,ROUND(ABS(R98)*(R96/100),2),ROUND(R98/(R96/100),2))</f>
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="S99" s="5"/>
       <c r="T99" s="5">
         <f>IF(T96&gt;0,ROUND(ABS(T98)*(T96/100),2),ROUND(T98/(T96/100),2))</f>
-        <v>0.56999999999999995</v>
+        <v>0.28999999999999998</v>
       </c>
       <c r="U99" s="5"/>
       <c r="V99" s="5">
         <f>IF(V96&gt;0,ROUND(ABS(V98)*(V96/100),2),ROUND(V98/(V96/100),2))</f>
-        <v>0.21</v>
+        <v>0.69</v>
       </c>
       <c r="W99" s="8">
         <f>SUM(D99:V99)</f>
-        <v>4.6099999999999994</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="100" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4352,22 +4362,22 @@
       <c r="C100" s="5"/>
       <c r="D100" s="5">
         <f>IF(D95=D93,-D98+D99,0)</f>
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="E100" s="5"/>
       <c r="F100" s="5">
         <f>IF(F95=F93,-F98+F99,0)</f>
-        <v>1.3599999999999999</v>
+        <v>0</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="5">
         <f>IF(H95=H93,-H98+H99,0)</f>
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="I100" s="5"/>
       <c r="J100" s="5">
         <f>IF(J95=J93,-J98+J99,0)</f>
-        <v>1.3599999999999999</v>
+        <v>0</v>
       </c>
       <c r="K100" s="5"/>
       <c r="L100" s="5">
@@ -4377,12 +4387,12 @@
       <c r="M100" s="5"/>
       <c r="N100" s="5">
         <f>IF(N95=N93,-N98+N99,0)</f>
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="O100" s="5"/>
       <c r="P100" s="5">
         <f>IF(P95=P93,-P98+P99,0)</f>
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q100" s="5"/>
       <c r="R100" s="5">
@@ -4397,17 +4407,17 @@
       <c r="U100" s="5"/>
       <c r="V100" s="6">
         <f>IF(V95=V93,-V98+V99,0)</f>
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W100" s="9">
         <f>SUM(D100:V100)</f>
-        <v>10.23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="W101" s="7">
         <f>W98+W100</f>
-        <v>0.23000000000000043</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="102" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -4417,23 +4427,23 @@
       <c r="V102" s="13"/>
       <c r="W102" s="11">
         <f>W85+W101</f>
-        <v>1.5500000000000007</v>
+        <v>-8.68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="U51:V51"/>
+    <mergeCell ref="D1:V1"/>
+    <mergeCell ref="D18:V18"/>
+    <mergeCell ref="D35:V35"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="U34:V34"/>
     <mergeCell ref="D86:V86"/>
     <mergeCell ref="U102:V102"/>
     <mergeCell ref="D69:V69"/>
     <mergeCell ref="U85:V85"/>
     <mergeCell ref="D52:V52"/>
     <mergeCell ref="U68:V68"/>
-    <mergeCell ref="U51:V51"/>
-    <mergeCell ref="D1:V1"/>
-    <mergeCell ref="D18:V18"/>
-    <mergeCell ref="D35:V35"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="U34:V34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Git-Folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EB6499A-1643-4216-84F4-12E37C95FA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6552D93-8C8B-47D0-AFEF-7A8E58620BF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="79">
   <si>
     <t>Goals</t>
   </si>
@@ -897,10 +897,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1285,27 +1285,27 @@
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D2" t="s">
@@ -1705,37 +1705,37 @@
       </c>
     </row>
     <row r="17" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V17" s="13"/>
+      <c r="V17" s="12"/>
       <c r="W17" s="11">
         <f>W16</f>
         <v>-0.74000000000000021</v>
       </c>
     </row>
     <row r="18" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
     </row>
     <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D19" t="s">
@@ -2175,37 +2175,37 @@
       </c>
     </row>
     <row r="34" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U34" s="13" t="s">
+      <c r="U34" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V34" s="13"/>
+      <c r="V34" s="12"/>
       <c r="W34" s="11">
         <f>W33+W17</f>
         <v>-0.58000000000000007</v>
       </c>
     </row>
     <row r="35" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D35" s="12" t="s">
+      <c r="D35" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
     </row>
     <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D36" t="s">
@@ -2731,37 +2731,37 @@
       </c>
     </row>
     <row r="51" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U51" s="13" t="s">
+      <c r="U51" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V51" s="13"/>
+      <c r="V51" s="12"/>
       <c r="W51" s="11">
         <f>W34+W50</f>
         <v>0.82000000000000028</v>
       </c>
     </row>
     <row r="52" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D52" s="12" t="s">
+      <c r="D52" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="12"/>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="12"/>
-      <c r="U52" s="12"/>
-      <c r="V52" s="12"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13"/>
     </row>
     <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D53" t="s">
@@ -3301,37 +3301,37 @@
       </c>
     </row>
     <row r="68" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U68" s="13" t="s">
+      <c r="U68" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V68" s="13"/>
+      <c r="V68" s="12"/>
       <c r="W68" s="11">
         <f>W51+W67</f>
         <v>1.0899999999999999</v>
       </c>
     </row>
     <row r="69" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D69" s="12" t="s">
+      <c r="D69" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="E69" s="12"/>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-      <c r="O69" s="12"/>
-      <c r="P69" s="12"/>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="12"/>
+      <c r="E69" s="13"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+      <c r="P69" s="13"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="13"/>
+      <c r="U69" s="13"/>
+      <c r="V69" s="13"/>
     </row>
     <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D70" t="s">
@@ -3871,37 +3871,37 @@
       </c>
     </row>
     <row r="85" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U85" s="13" t="s">
+      <c r="U85" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V85" s="13"/>
+      <c r="V85" s="12"/>
       <c r="W85" s="11">
         <f>W68+W84</f>
         <v>1.3200000000000003</v>
       </c>
     </row>
     <row r="86" spans="1:23" ht="24" x14ac:dyDescent="0.4">
-      <c r="D86" s="12" t="s">
+      <c r="D86" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="E86" s="12"/>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="12"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="12"/>
-      <c r="V86" s="12"/>
+      <c r="E86" s="13"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+      <c r="P86" s="13"/>
+      <c r="Q86" s="13"/>
+      <c r="R86" s="13"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="13"/>
+      <c r="U86" s="13"/>
+      <c r="V86" s="13"/>
     </row>
     <row r="87" spans="1:23" x14ac:dyDescent="0.25">
       <c r="D87" t="s">
@@ -4182,15 +4182,25 @@
         <v>16</v>
       </c>
       <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
+      <c r="D95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
+      <c r="F95" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
+      <c r="H95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
+      <c r="J95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="K95" s="5"/>
-      <c r="L95" s="5"/>
+      <c r="L95" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="M95" s="5"/>
       <c r="N95" s="5"/>
       <c r="O95" s="5"/>
@@ -4382,7 +4392,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5">
         <f>IF(L95=L93,-L98+L99,0)</f>
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M100" s="5"/>
       <c r="N100" s="5">
@@ -4411,39 +4421,39 @@
       </c>
       <c r="W100" s="9">
         <f>SUM(D100:V100)</f>
-        <v>0</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="101" spans="2:23" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="W101" s="7">
         <f>W98+W100</f>
-        <v>-10</v>
+        <v>-8.52</v>
       </c>
     </row>
     <row r="102" spans="2:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="U102" s="13" t="s">
+      <c r="U102" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="V102" s="13"/>
+      <c r="V102" s="12"/>
       <c r="W102" s="11">
         <f>W85+W101</f>
-        <v>-8.68</v>
+        <v>-7.1999999999999993</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="D86:V86"/>
+    <mergeCell ref="U102:V102"/>
+    <mergeCell ref="D69:V69"/>
+    <mergeCell ref="U85:V85"/>
+    <mergeCell ref="D52:V52"/>
+    <mergeCell ref="U68:V68"/>
     <mergeCell ref="U51:V51"/>
     <mergeCell ref="D1:V1"/>
     <mergeCell ref="D18:V18"/>
     <mergeCell ref="D35:V35"/>
     <mergeCell ref="U17:V17"/>
     <mergeCell ref="U34:V34"/>
-    <mergeCell ref="D86:V86"/>
-    <mergeCell ref="U102:V102"/>
-    <mergeCell ref="D69:V69"/>
-    <mergeCell ref="U85:V85"/>
-    <mergeCell ref="D52:V52"/>
-    <mergeCell ref="U68:V68"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29523"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattc\git-folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A89CDEF-687D-46A9-B397-73441ACBA518}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C19D062F-42CC-4F98-8CCF-C1C4DB6DEA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="16440" windowHeight="28320" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
   <sheets>
     <sheet name="Predictions 2(Records)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="486" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="117">
   <si>
     <t>Goals</t>
   </si>
@@ -98,6 +101,9 @@
     <t>Total Payout:</t>
   </si>
   <si>
+    <t>Current Profit/Loss:</t>
+  </si>
+  <si>
     <t>Match Week 7</t>
   </si>
   <si>
@@ -140,18 +146,18 @@
     <t>NOF vs CHE</t>
   </si>
   <si>
+    <t>MCI vs EVE</t>
+  </si>
+  <si>
+    <t>BUR vs LEE</t>
+  </si>
+  <si>
+    <t>CRY vs BOU</t>
+  </si>
+  <si>
     <t>BHA vs NCU</t>
   </si>
   <si>
-    <t>BUR vs LEE</t>
-  </si>
-  <si>
-    <t>CRY vs BOU</t>
-  </si>
-  <si>
-    <t>MCI vs EVE</t>
-  </si>
-  <si>
     <t>SUN vs WOL</t>
   </si>
   <si>
@@ -167,9 +173,6 @@
     <t>WHU vs BRE</t>
   </si>
   <si>
-    <t>Current Profit/Loss:</t>
-  </si>
-  <si>
     <t>Forgot to Place</t>
   </si>
   <si>
@@ -275,6 +278,9 @@
     <t>Match Week 12</t>
   </si>
   <si>
+    <t>Model:</t>
+  </si>
+  <si>
     <t>BUR vs CHE</t>
   </si>
   <si>
@@ -308,17 +314,86 @@
     <t>KNN</t>
   </si>
   <si>
-    <t>Model:</t>
+    <t>Did not bet this week</t>
   </si>
   <si>
     <t>XGB</t>
+  </si>
+  <si>
+    <t>Match Week 13</t>
+  </si>
+  <si>
+    <t>BRE vs BUR</t>
+  </si>
+  <si>
+    <t>MCI vs LEE</t>
+  </si>
+  <si>
+    <t>SUN vs BOU</t>
+  </si>
+  <si>
+    <t>EVE vs NCU</t>
+  </si>
+  <si>
+    <t>TOT vs FUL</t>
+  </si>
+  <si>
+    <t>CRY vs MUN</t>
+  </si>
+  <si>
+    <t>NOF vs BHA</t>
+  </si>
+  <si>
+    <t>AVL vs WOL</t>
+  </si>
+  <si>
+    <t>WHU vs LIV</t>
+  </si>
+  <si>
+    <t>CHE vs ARS</t>
+  </si>
+  <si>
+    <t>Did Not Calculate</t>
+  </si>
+  <si>
+    <t>Match Week 14 - Started using XGBoost for bets</t>
+  </si>
+  <si>
+    <t>FUL vs MCI</t>
+  </si>
+  <si>
+    <t>BOU vs EVE</t>
+  </si>
+  <si>
+    <t>NCU vs TOT</t>
+  </si>
+  <si>
+    <t>ARS vs BRE</t>
+  </si>
+  <si>
+    <t>BHA vs AVL</t>
+  </si>
+  <si>
+    <t>WOL vs NOF</t>
+  </si>
+  <si>
+    <t>BUR vs CRY</t>
+  </si>
+  <si>
+    <t>LIV vs SUN</t>
+  </si>
+  <si>
+    <t>LEE vs CHE</t>
+  </si>
+  <si>
+    <t>MUN vs WHU</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -926,7 +1001,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -944,6 +1019,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1320,10 +1398,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA341253-1EAB-4104-BE4B-374BC158237A}">
-  <dimension ref="A1:X121"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Z159"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:24" ht="24">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1349,7 +1430,7 @@
       <c r="V1" s="12"/>
       <c r="W1" s="12"/>
     </row>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:24">
       <c r="E2" t="s">
         <v>2</v>
       </c>
@@ -1381,7 +1462,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:24">
       <c r="B3">
         <v>3.5</v>
       </c>
@@ -1389,7 +1470,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:24">
       <c r="B4">
         <v>2.5</v>
       </c>
@@ -1397,7 +1478,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:24">
       <c r="B5">
         <v>3.5</v>
       </c>
@@ -1405,7 +1486,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:24">
       <c r="B6">
         <v>2.5</v>
       </c>
@@ -1413,7 +1494,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:24">
       <c r="C8" s="4" t="s">
         <v>12</v>
       </c>
@@ -1458,7 +1539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:24">
       <c r="C9" s="4" t="s">
         <v>15</v>
       </c>
@@ -1503,7 +1584,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:24">
       <c r="C10" s="2" t="s">
         <v>16</v>
       </c>
@@ -1538,7 +1619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:24">
       <c r="C11" s="4" t="s">
         <v>17</v>
       </c>
@@ -1583,7 +1664,7 @@
         <v>-330</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:24">
       <c r="C13" s="4" t="s">
         <v>18</v>
       </c>
@@ -1632,7 +1713,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:24">
       <c r="C14" s="4" t="s">
         <v>19</v>
       </c>
@@ -1681,7 +1762,7 @@
         <v>4.9799999999999995</v>
       </c>
     </row>
-    <row r="15" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:24" ht="15.75" thickBot="1">
       <c r="C15" s="4" t="s">
         <v>20</v>
       </c>
@@ -1740,15 +1821,15 @@
         <v>9.26</v>
       </c>
     </row>
-    <row r="16" spans="2:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="X16" s="10">
         <f>X13+X15</f>
         <v>-0.74000000000000021</v>
       </c>
     </row>
-    <row r="17" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:24" ht="15.75" thickBot="1">
       <c r="V17" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W17" s="13"/>
       <c r="X17" s="11">
@@ -1756,9 +1837,9 @@
         <v>-0.74000000000000021</v>
       </c>
     </row>
-    <row r="18" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:24" ht="24">
       <c r="E18" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F18" s="12"/>
       <c r="G18" s="12"/>
@@ -1779,39 +1860,39 @@
       <c r="V18" s="12"/>
       <c r="W18" s="12"/>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:24">
       <c r="E19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I19" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="O19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="Q19" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S19" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="U19" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="W19" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="2:24">
       <c r="B20">
         <v>3.5</v>
       </c>
@@ -1849,7 +1930,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:24">
       <c r="B21">
         <v>2.5</v>
       </c>
@@ -1857,7 +1938,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="22" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:24">
       <c r="B22">
         <v>3.5</v>
       </c>
@@ -1865,7 +1946,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:24">
       <c r="B23">
         <v>2.5</v>
       </c>
@@ -1873,7 +1954,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:24">
       <c r="C25" s="4" t="s">
         <v>12</v>
       </c>
@@ -1883,7 +1964,7 @@
       </c>
       <c r="F25" s="5"/>
       <c r="G25" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="5"/>
       <c r="I25" s="5" t="s">
@@ -1918,7 +1999,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:24">
       <c r="C26" s="4" t="s">
         <v>15</v>
       </c>
@@ -1963,7 +2044,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:24">
       <c r="C27" s="4" t="s">
         <v>16</v>
       </c>
@@ -2008,7 +2089,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:24">
       <c r="C28" s="4" t="s">
         <v>17</v>
       </c>
@@ -2053,7 +2134,7 @@
         <v>-175</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:24">
       <c r="C30" s="4" t="s">
         <v>18</v>
       </c>
@@ -2102,7 +2183,7 @@
         <v>-9</v>
       </c>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:24">
       <c r="C31" s="4" t="s">
         <v>19</v>
       </c>
@@ -2151,7 +2232,7 @@
         <v>4.67</v>
       </c>
     </row>
-    <row r="32" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:24" ht="15.75" thickBot="1">
       <c r="C32" s="4" t="s">
         <v>20</v>
       </c>
@@ -2210,15 +2291,15 @@
         <v>9.16</v>
       </c>
     </row>
-    <row r="33" spans="2:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="X33" s="7">
         <f>X30+X32</f>
         <v>0.16000000000000014</v>
       </c>
     </row>
-    <row r="34" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:24" ht="15.75" thickBot="1">
       <c r="V34" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W34" s="13"/>
       <c r="X34" s="11">
@@ -2226,9 +2307,9 @@
         <v>-0.58000000000000007</v>
       </c>
     </row>
-    <row r="35" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="35" spans="2:24" ht="24">
       <c r="E35" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F35" s="12"/>
       <c r="G35" s="12"/>
@@ -2249,39 +2330,39 @@
       <c r="V35" s="12"/>
       <c r="W35" s="12"/>
     </row>
-    <row r="36" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:24">
       <c r="E36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G36" t="s">
+        <v>36</v>
+      </c>
+      <c r="I36" t="s">
+        <v>37</v>
+      </c>
+      <c r="K36" t="s">
         <v>38</v>
       </c>
-      <c r="I36" t="s">
-        <v>36</v>
-      </c>
-      <c r="K36" t="s">
-        <v>37</v>
-      </c>
       <c r="M36" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="O36" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q36" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U36" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="W36" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24">
       <c r="B37">
         <v>3.5</v>
       </c>
@@ -2319,7 +2400,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:24">
       <c r="B38">
         <v>2.5</v>
       </c>
@@ -2357,7 +2438,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:24">
       <c r="B39">
         <v>3.5</v>
       </c>
@@ -2395,7 +2476,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:24">
       <c r="B40">
         <v>2.5</v>
       </c>
@@ -2433,7 +2514,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:24">
       <c r="C42" s="4" t="s">
         <v>12</v>
       </c>
@@ -2478,7 +2559,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:24">
       <c r="C43" s="4" t="s">
         <v>15</v>
       </c>
@@ -2523,7 +2604,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:24">
       <c r="C44" s="4" t="s">
         <v>16</v>
       </c>
@@ -2568,7 +2649,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:24">
       <c r="C45" s="4" t="s">
         <v>17</v>
       </c>
@@ -2613,7 +2694,7 @@
         <v>-275</v>
       </c>
     </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:24">
       <c r="C47" s="4" t="s">
         <v>18</v>
       </c>
@@ -2648,7 +2729,7 @@
         <v>-3</v>
       </c>
     </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:24">
       <c r="C48" s="4" t="s">
         <v>19</v>
       </c>
@@ -2707,7 +2788,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="49" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:24" ht="15.75" thickBot="1">
       <c r="C49" s="4" t="s">
         <v>20</v>
       </c>
@@ -2766,15 +2847,15 @@
         <v>4.4000000000000004</v>
       </c>
     </row>
-    <row r="50" spans="2:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="X50" s="7">
         <f>X47+X49</f>
         <v>1.4000000000000004</v>
       </c>
     </row>
-    <row r="51" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:24" ht="15.75" thickBot="1">
       <c r="V51" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W51" s="13"/>
       <c r="X51" s="11">
@@ -2782,7 +2863,7 @@
         <v>0.82000000000000028</v>
       </c>
     </row>
-    <row r="52" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="52" spans="2:24" ht="24">
       <c r="E52" s="12" t="s">
         <v>46</v>
       </c>
@@ -2805,7 +2886,7 @@
       <c r="V52" s="12"/>
       <c r="W52" s="12"/>
     </row>
-    <row r="53" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:24">
       <c r="E53" t="s">
         <v>47</v>
       </c>
@@ -2837,7 +2918,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:24">
       <c r="B54">
         <v>3.5</v>
       </c>
@@ -2875,7 +2956,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="55" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:24">
       <c r="B55">
         <v>2.5</v>
       </c>
@@ -2913,7 +2994,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="56" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:24">
       <c r="B56">
         <v>3.5</v>
       </c>
@@ -2951,7 +3032,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="57" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:24">
       <c r="B57">
         <v>2.5</v>
       </c>
@@ -2989,7 +3070,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:24">
       <c r="C59" s="4" t="s">
         <v>12</v>
       </c>
@@ -3034,7 +3115,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="60" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:24">
       <c r="C60" s="4" t="s">
         <v>15</v>
       </c>
@@ -3079,7 +3160,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="61" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:24">
       <c r="C61" s="4" t="s">
         <v>16</v>
       </c>
@@ -3124,7 +3205,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:24">
       <c r="C62" s="4" t="s">
         <v>17</v>
       </c>
@@ -3169,7 +3250,7 @@
         <v>-310</v>
       </c>
     </row>
-    <row r="64" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:24">
       <c r="C64" s="4" t="s">
         <v>18</v>
       </c>
@@ -3218,7 +3299,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:24">
       <c r="C65" s="4" t="s">
         <v>19</v>
       </c>
@@ -3277,7 +3358,7 @@
         <v>4.63</v>
       </c>
     </row>
-    <row r="66" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:24" ht="15.75" thickBot="1">
       <c r="C66" s="4" t="s">
         <v>20</v>
       </c>
@@ -3336,15 +3417,15 @@
         <v>10.27</v>
       </c>
     </row>
-    <row r="67" spans="2:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="X67" s="7">
         <f>X64+X66</f>
         <v>0.26999999999999957</v>
       </c>
     </row>
-    <row r="68" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:24" ht="15.75" thickBot="1">
       <c r="V68" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W68" s="13"/>
       <c r="X68" s="11">
@@ -3352,7 +3433,7 @@
         <v>1.0899999999999999</v>
       </c>
     </row>
-    <row r="69" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="69" spans="2:24" ht="24">
       <c r="E69" s="12" t="s">
         <v>57</v>
       </c>
@@ -3375,7 +3456,7 @@
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
     </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:24">
       <c r="E70" t="s">
         <v>58</v>
       </c>
@@ -3407,7 +3488,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:24">
       <c r="B71">
         <v>3.5</v>
       </c>
@@ -3445,7 +3526,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:24">
       <c r="B72">
         <v>2.5</v>
       </c>
@@ -3483,7 +3564,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:24">
       <c r="B73">
         <v>3.5</v>
       </c>
@@ -3521,7 +3602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:24">
       <c r="B74">
         <v>2.5</v>
       </c>
@@ -3559,7 +3640,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:24">
       <c r="C76" s="4" t="s">
         <v>12</v>
       </c>
@@ -3604,7 +3685,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:24">
       <c r="C77" s="4" t="s">
         <v>15</v>
       </c>
@@ -3649,7 +3730,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="78" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:24">
       <c r="C78" s="4" t="s">
         <v>16</v>
       </c>
@@ -3694,7 +3775,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:24">
       <c r="C79" s="4" t="s">
         <v>17</v>
       </c>
@@ -3739,7 +3820,7 @@
         <v>-475</v>
       </c>
     </row>
-    <row r="81" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:24">
       <c r="C81" s="4" t="s">
         <v>18</v>
       </c>
@@ -3788,7 +3869,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="82" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:24">
       <c r="C82" s="4" t="s">
         <v>19</v>
       </c>
@@ -3847,7 +3928,7 @@
         <v>4.6099999999999994</v>
       </c>
     </row>
-    <row r="83" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:24" ht="15.75" thickBot="1">
       <c r="C83" s="4" t="s">
         <v>20</v>
       </c>
@@ -3906,15 +3987,15 @@
         <v>10.23</v>
       </c>
     </row>
-    <row r="84" spans="2:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:24" ht="16.5" thickTop="1" thickBot="1">
       <c r="X84" s="7">
         <f>X81+X83</f>
         <v>0.23000000000000043</v>
       </c>
     </row>
-    <row r="85" spans="2:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:24" ht="15.75" thickBot="1">
       <c r="V85" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W85" s="13"/>
       <c r="X85" s="11">
@@ -3922,7 +4003,7 @@
         <v>1.3200000000000003</v>
       </c>
     </row>
-    <row r="86" spans="2:24" ht="24" x14ac:dyDescent="0.4">
+    <row r="86" spans="2:24" ht="24">
       <c r="E86" s="12" t="s">
         <v>68</v>
       </c>
@@ -3945,7 +4026,7 @@
       <c r="V86" s="12"/>
       <c r="W86" s="12"/>
     </row>
-    <row r="87" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:24">
       <c r="E87" t="s">
         <v>69</v>
       </c>
@@ -3977,7 +4058,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="88" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:24">
       <c r="B88">
         <v>3.5</v>
       </c>
@@ -4015,7 +4096,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="89" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:24">
       <c r="B89">
         <v>2.5</v>
       </c>
@@ -4053,7 +4134,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:24">
       <c r="B90">
         <v>3.5</v>
       </c>
@@ -4091,7 +4172,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:24">
       <c r="B91">
         <v>2.5</v>
       </c>
@@ -4129,7 +4210,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="93" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:24">
       <c r="C93" s="4" t="s">
         <v>12</v>
       </c>
@@ -4174,7 +4255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="94" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:24">
       <c r="C94" s="4" t="s">
         <v>15</v>
       </c>
@@ -4219,7 +4300,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="95" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:24">
       <c r="C95" s="4" t="s">
         <v>16</v>
       </c>
@@ -4244,17 +4325,27 @@
         <v>13</v>
       </c>
       <c r="N95" s="5"/>
-      <c r="O95" s="5"/>
+      <c r="O95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
+      <c r="Q95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="R95" s="5"/>
-      <c r="S95" s="5"/>
+      <c r="S95" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="T95" s="5"/>
-      <c r="U95" s="5"/>
+      <c r="U95" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="V95" s="5"/>
-      <c r="W95" s="6"/>
-    </row>
-    <row r="96" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="W95" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="96" spans="2:24">
       <c r="C96" s="4" t="s">
         <v>17</v>
       </c>
@@ -4299,7 +4390,7 @@
         <v>-145</v>
       </c>
     </row>
-    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:26">
       <c r="C98" s="4" t="s">
         <v>18</v>
       </c>
@@ -4348,7 +4439,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:26">
       <c r="C99" s="4" t="s">
         <v>19</v>
       </c>
@@ -4407,7 +4498,7 @@
         <v>5.32</v>
       </c>
     </row>
-    <row r="100" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:26" ht="15.75" thickBot="1">
       <c r="C100" s="4" t="s">
         <v>20</v>
       </c>
@@ -4444,12 +4535,12 @@
       <c r="P100" s="5"/>
       <c r="Q100" s="5">
         <f>IF(Q95=Q93,-Q98+Q99,0)</f>
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="R100" s="5"/>
       <c r="S100" s="5">
         <f>IF(S95=S93,-S98+S99,0)</f>
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="T100" s="5"/>
       <c r="U100" s="5">
@@ -4459,30 +4550,30 @@
       <c r="V100" s="5"/>
       <c r="W100" s="6">
         <f>IF(W95=W93,-W98+W99,0)</f>
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="X100" s="9">
         <f>SUM(E100:W100)</f>
-        <v>1.48</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>6.3699999999999992</v>
+      </c>
+    </row>
+    <row r="101" spans="1:26" ht="16.5" thickTop="1" thickBot="1">
       <c r="X101" s="7">
         <f>X98+X100</f>
-        <v>-8.52</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>-3.6300000000000008</v>
+      </c>
+    </row>
+    <row r="102" spans="1:26" ht="15.75" thickBot="1">
       <c r="V102" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W102" s="13"/>
       <c r="X102" s="11">
         <f>X85+X101</f>
-        <v>-7.1999999999999993</v>
-      </c>
-    </row>
-    <row r="103" spans="1:24" ht="24" x14ac:dyDescent="0.4">
+        <v>-2.3100000000000005</v>
+      </c>
+    </row>
+    <row r="103" spans="1:26" ht="24">
       <c r="E103" s="12" t="s">
         <v>79</v>
       </c>
@@ -4505,44 +4596,44 @@
       <c r="V103" s="12"/>
       <c r="W103" s="12"/>
     </row>
-    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:26">
       <c r="A104" t="s">
+        <v>80</v>
+      </c>
+      <c r="E104" t="s">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s">
+        <v>82</v>
+      </c>
+      <c r="I104" t="s">
+        <v>83</v>
+      </c>
+      <c r="K104" t="s">
+        <v>84</v>
+      </c>
+      <c r="M104" t="s">
+        <v>85</v>
+      </c>
+      <c r="O104" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>87</v>
+      </c>
+      <c r="S104" t="s">
+        <v>88</v>
+      </c>
+      <c r="U104" t="s">
+        <v>89</v>
+      </c>
+      <c r="W104" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="105" spans="1:26">
+      <c r="A105" t="s">
         <v>91</v>
-      </c>
-      <c r="E104" t="s">
-        <v>80</v>
-      </c>
-      <c r="G104" t="s">
-        <v>81</v>
-      </c>
-      <c r="I104" t="s">
-        <v>82</v>
-      </c>
-      <c r="K104" t="s">
-        <v>83</v>
-      </c>
-      <c r="M104" t="s">
-        <v>84</v>
-      </c>
-      <c r="O104" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q104" t="s">
-        <v>86</v>
-      </c>
-      <c r="S104" t="s">
-        <v>87</v>
-      </c>
-      <c r="U104" t="s">
-        <v>88</v>
-      </c>
-      <c r="W104" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>90</v>
       </c>
       <c r="B105">
         <v>3.5</v>
@@ -4580,10 +4671,14 @@
       <c r="W105" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y105" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z105" s="14"/>
+    </row>
+    <row r="106" spans="1:26">
       <c r="A106" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B106">
         <v>2.5</v>
@@ -4621,10 +4716,12 @@
       <c r="W106" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y106" s="14"/>
+      <c r="Z106" s="14"/>
+    </row>
+    <row r="107" spans="1:26">
       <c r="A107" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B107">
         <v>3.5</v>
@@ -4662,10 +4759,12 @@
       <c r="W107" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y107" s="14"/>
+      <c r="Z107" s="14"/>
+    </row>
+    <row r="108" spans="1:26">
       <c r="A108" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B108">
         <v>2.5</v>
@@ -4703,10 +4802,12 @@
       <c r="W108" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y108" s="14"/>
+      <c r="Z108" s="14"/>
+    </row>
+    <row r="109" spans="1:26">
       <c r="A109" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B109">
         <v>3.5</v>
@@ -4741,10 +4842,12 @@
       <c r="W109" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y109" s="14"/>
+      <c r="Z109" s="14"/>
+    </row>
+    <row r="110" spans="1:26">
       <c r="A110" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B110">
         <v>2.5</v>
@@ -4779,33 +4882,55 @@
       <c r="W110" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y110" s="14"/>
+      <c r="Z110" s="14"/>
+    </row>
+    <row r="112" spans="1:26">
       <c r="C112" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D112" s="5"/>
-      <c r="E112" s="5"/>
+      <c r="E112" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="F112" s="5"/>
-      <c r="G112" s="5"/>
+      <c r="G112" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
+      <c r="I112" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="J112" s="5"/>
-      <c r="K112" s="5"/>
+      <c r="K112" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="L112" s="5"/>
-      <c r="M112" s="5"/>
+      <c r="M112" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="N112" s="5"/>
-      <c r="O112" s="5"/>
+      <c r="O112" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="P112" s="5"/>
-      <c r="Q112" s="5"/>
+      <c r="Q112" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="R112" s="5"/>
-      <c r="S112" s="5"/>
+      <c r="S112" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="T112" s="5"/>
-      <c r="U112" s="5"/>
+      <c r="U112" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="V112" s="5"/>
-      <c r="W112" s="6"/>
-    </row>
-    <row r="113" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="W112" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24">
       <c r="C113" s="4" t="s">
         <v>15</v>
       </c>
@@ -4819,7 +4944,7 @@
       </c>
       <c r="H113" s="5"/>
       <c r="I113" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5">
@@ -4831,15 +4956,15 @@
       </c>
       <c r="N113" s="5"/>
       <c r="O113" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="P113" s="5"/>
       <c r="Q113" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="R113" s="5"/>
       <c r="S113" s="5">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="T113" s="5"/>
       <c r="U113" s="5">
@@ -4850,57 +4975,93 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="114" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:24">
       <c r="C114" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D114" s="5"/>
-      <c r="E114" s="5"/>
+      <c r="E114" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="F114" s="5"/>
-      <c r="G114" s="5"/>
+      <c r="G114" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
+      <c r="I114" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="J114" s="5"/>
-      <c r="K114" s="5"/>
+      <c r="K114" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="L114" s="5"/>
-      <c r="M114" s="5"/>
+      <c r="M114" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="N114" s="5"/>
-      <c r="O114" s="5"/>
+      <c r="O114" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="P114" s="5"/>
-      <c r="Q114" s="5"/>
+      <c r="Q114" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="R114" s="5"/>
-      <c r="S114" s="5"/>
+      <c r="S114" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="T114" s="5"/>
       <c r="U114" s="5"/>
       <c r="V114" s="5"/>
       <c r="W114" s="6"/>
     </row>
-    <row r="115" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:24">
       <c r="C115" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D115" s="5"/>
-      <c r="E115" s="5"/>
+      <c r="E115" s="5">
+        <v>-255</v>
+      </c>
       <c r="F115" s="5"/>
-      <c r="G115" s="5"/>
+      <c r="G115" s="5">
+        <v>-375</v>
+      </c>
       <c r="H115" s="5"/>
-      <c r="I115" s="5"/>
+      <c r="I115" s="5">
+        <v>-145</v>
+      </c>
       <c r="J115" s="5"/>
-      <c r="K115" s="5"/>
+      <c r="K115" s="5">
+        <v>-400</v>
+      </c>
       <c r="L115" s="5"/>
-      <c r="M115" s="5"/>
+      <c r="M115" s="5">
+        <v>-175</v>
+      </c>
       <c r="N115" s="5"/>
-      <c r="O115" s="5"/>
+      <c r="O115" s="5">
+        <v>120</v>
+      </c>
       <c r="P115" s="5"/>
-      <c r="Q115" s="5"/>
+      <c r="Q115" s="5">
+        <v>-220</v>
+      </c>
       <c r="R115" s="5"/>
-      <c r="S115" s="5"/>
+      <c r="S115" s="5">
+        <v>110</v>
+      </c>
       <c r="T115" s="5"/>
-      <c r="U115" s="5"/>
+      <c r="U115" s="5">
+        <v>-255</v>
+      </c>
       <c r="V115" s="5"/>
-      <c r="W115" s="6"/>
-    </row>
-    <row r="117" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="W115" s="6">
+        <v>-250</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24">
       <c r="C117" s="4" t="s">
         <v>18</v>
       </c>
@@ -4949,156 +5110,1444 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="118" spans="3:24" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:24">
       <c r="C118" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D118" s="5"/>
-      <c r="E118" s="5" t="e">
+      <c r="E118" s="5">
         <f>IF(E115&gt;0,ROUND(ABS(E117)*(E115/100),2),ROUND(E117/(E115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.39</v>
       </c>
       <c r="F118" s="5"/>
-      <c r="G118" s="5" t="e">
+      <c r="G118" s="5">
         <f>IF(G115&gt;0,ROUND(ABS(G117)*(G115/100),2),ROUND(G117/(G115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.27</v>
       </c>
       <c r="H118" s="5"/>
-      <c r="I118" s="5" t="e">
+      <c r="I118" s="5">
         <f>IF(I115&gt;0,ROUND(ABS(I117)*(I115/100),2),ROUND(I117/(I115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.69</v>
       </c>
       <c r="J118" s="5"/>
-      <c r="K118" s="5" t="e">
+      <c r="K118" s="5">
         <f>IF(K115&gt;0,ROUND(ABS(K117)*(K115/100),2),ROUND(K117/(K115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.25</v>
       </c>
       <c r="L118" s="5"/>
-      <c r="M118" s="5" t="e">
+      <c r="M118" s="5">
         <f>IF(M115&gt;0,ROUND(ABS(M117)*(M115/100),2),ROUND(M117/(M115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N118" s="5"/>
-      <c r="O118" s="5" t="e">
+      <c r="O118" s="5">
         <f>IF(O115&gt;0,ROUND(ABS(O117)*(O115/100),2),ROUND(O117/(O115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>1.2</v>
       </c>
       <c r="P118" s="5"/>
-      <c r="Q118" s="5" t="e">
+      <c r="Q118" s="5">
         <f>IF(Q115&gt;0,ROUND(ABS(Q117)*(Q115/100),2),ROUND(Q117/(Q115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.45</v>
       </c>
       <c r="R118" s="5"/>
-      <c r="S118" s="5" t="e">
+      <c r="S118" s="5">
         <f>IF(S115&gt;0,ROUND(ABS(S117)*(S115/100),2),ROUND(S117/(S115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="T118" s="5"/>
-      <c r="U118" s="5" t="e">
+      <c r="U118" s="5">
         <f>IF(U115&gt;0,ROUND(ABS(U117)*(U115/100),2),ROUND(U117/(U115/100),2))</f>
-        <v>#DIV/0!</v>
+        <v>0.39</v>
       </c>
       <c r="V118" s="5"/>
-      <c r="W118" s="5" t="e">
+      <c r="W118" s="5">
         <f>IF(W115&gt;0,ROUND(ABS(W117)*(W115/100),2),ROUND(W117/(W115/100),2))</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X118" s="8" t="e">
+        <v>0.4</v>
+      </c>
+      <c r="X118" s="8">
         <f>SUM(E118:W118)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="119" spans="3:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>5.71</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" ht="15.75" thickBot="1">
       <c r="C119" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D119" s="5"/>
-      <c r="E119" s="5" t="e">
+      <c r="E119" s="5">
         <f>IF(E114=E112,-E117+E118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.3900000000000001</v>
       </c>
       <c r="F119" s="5"/>
-      <c r="G119" s="5" t="e">
+      <c r="G119" s="5">
         <f>IF(G114=G112,-G117+G118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.27</v>
       </c>
       <c r="H119" s="5"/>
-      <c r="I119" s="5" t="e">
+      <c r="I119" s="5">
         <f>IF(I114=I112,-I117+I118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.69</v>
       </c>
       <c r="J119" s="5"/>
-      <c r="K119" s="5" t="e">
+      <c r="K119" s="5">
         <f>IF(K114=K112,-K117+K118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.25</v>
       </c>
       <c r="L119" s="5"/>
-      <c r="M119" s="5" t="e">
+      <c r="M119" s="5">
         <f>IF(M114=M112,-M117+M118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.5699999999999998</v>
       </c>
       <c r="N119" s="5"/>
-      <c r="O119" s="5" t="e">
+      <c r="O119" s="5">
         <f>IF(O114=O112,-O117+O118,0)</f>
-        <v>#DIV/0!</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="P119" s="5"/>
-      <c r="Q119" s="5" t="e">
+      <c r="Q119" s="5">
         <f>IF(Q114=Q112,-Q117+Q118,0)</f>
-        <v>#DIV/0!</v>
+        <v>1.45</v>
       </c>
       <c r="R119" s="5"/>
-      <c r="S119" s="5" t="e">
+      <c r="S119" s="5">
         <f>IF(S114=S112,-S117+S118,0)</f>
-        <v>#DIV/0!</v>
+        <v>2.1</v>
       </c>
       <c r="T119" s="5"/>
-      <c r="U119" s="5" t="e">
+      <c r="U119" s="5">
         <f>IF(U114=U112,-U117+U118,0)</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="V119" s="5"/>
-      <c r="W119" s="6" t="e">
+      <c r="W119" s="6">
         <f>IF(W114=W112,-W117+W118,0)</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="X119" s="9" t="e">
+        <v>0</v>
+      </c>
+      <c r="X119" s="9">
         <f>SUM(E119:W119)</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="120" spans="3:24" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="X120" s="7" t="e">
+        <v>12.92</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" ht="16.5" thickTop="1" thickBot="1">
+      <c r="X120" s="7">
         <f>X117+X119</f>
-        <v>#DIV/0!</v>
-      </c>
-    </row>
-    <row r="121" spans="3:24" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>2.92</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24">
       <c r="V121" s="13" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="W121" s="13"/>
-      <c r="X121" s="11" t="e">
+      <c r="X121" s="11">
         <f>X102+X120</f>
-        <v>#DIV/0!</v>
+        <v>0.60999999999999943</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" ht="24">
+      <c r="E122" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F122" s="12"/>
+      <c r="G122" s="12"/>
+      <c r="H122" s="12"/>
+      <c r="I122" s="12"/>
+      <c r="J122" s="12"/>
+      <c r="K122" s="12"/>
+      <c r="L122" s="12"/>
+      <c r="M122" s="12"/>
+      <c r="N122" s="12"/>
+      <c r="O122" s="12"/>
+      <c r="P122" s="12"/>
+      <c r="Q122" s="12"/>
+      <c r="R122" s="12"/>
+      <c r="S122" s="12"/>
+      <c r="T122" s="12"/>
+      <c r="U122" s="12"/>
+      <c r="V122" s="12"/>
+      <c r="W122" s="12"/>
+    </row>
+    <row r="123" spans="1:24">
+      <c r="A123" t="s">
+        <v>80</v>
+      </c>
+      <c r="E123" t="s">
+        <v>95</v>
+      </c>
+      <c r="G123" t="s">
+        <v>96</v>
+      </c>
+      <c r="I123" t="s">
+        <v>97</v>
+      </c>
+      <c r="K123" t="s">
+        <v>98</v>
+      </c>
+      <c r="M123" t="s">
+        <v>99</v>
+      </c>
+      <c r="O123" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>101</v>
+      </c>
+      <c r="S123" t="s">
+        <v>102</v>
+      </c>
+      <c r="U123" t="s">
+        <v>103</v>
+      </c>
+      <c r="W123" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24">
+      <c r="A124" t="s">
+        <v>91</v>
+      </c>
+      <c r="B124">
+        <v>3.5</v>
+      </c>
+      <c r="C124" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E124" t="s">
+        <v>13</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="I124" t="s">
+        <v>13</v>
+      </c>
+      <c r="K124" t="s">
+        <v>13</v>
+      </c>
+      <c r="M124" t="s">
+        <v>13</v>
+      </c>
+      <c r="O124" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>13</v>
+      </c>
+      <c r="S124" t="s">
+        <v>13</v>
+      </c>
+      <c r="U124" t="s">
+        <v>13</v>
+      </c>
+      <c r="W124" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24">
+      <c r="A125" t="s">
+        <v>91</v>
+      </c>
+      <c r="B125">
+        <v>2.5</v>
+      </c>
+      <c r="C125" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E125" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F125" s="13"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
+      <c r="I125" s="13"/>
+      <c r="J125" s="13"/>
+      <c r="K125" s="13"/>
+      <c r="L125" s="13"/>
+      <c r="M125" s="13"/>
+      <c r="N125" s="13"/>
+      <c r="O125" s="13"/>
+      <c r="P125" s="13"/>
+      <c r="Q125" s="13"/>
+      <c r="R125" s="13"/>
+      <c r="S125" s="13"/>
+      <c r="T125" s="13"/>
+      <c r="U125" s="13"/>
+      <c r="V125" s="13"/>
+      <c r="W125" s="13"/>
+    </row>
+    <row r="126" spans="1:24">
+      <c r="A126" t="s">
+        <v>91</v>
+      </c>
+      <c r="B126">
+        <v>3.5</v>
+      </c>
+      <c r="C126" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E126" t="s">
+        <v>13</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="I126" t="s">
+        <v>13</v>
+      </c>
+      <c r="K126" t="s">
+        <v>13</v>
+      </c>
+      <c r="M126" t="s">
+        <v>13</v>
+      </c>
+      <c r="O126" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>13</v>
+      </c>
+      <c r="S126" t="s">
+        <v>14</v>
+      </c>
+      <c r="U126" t="s">
+        <v>13</v>
+      </c>
+      <c r="W126" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24">
+      <c r="A127" t="s">
+        <v>91</v>
+      </c>
+      <c r="B127">
+        <v>2.5</v>
+      </c>
+      <c r="C127" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E127" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="F127" s="13"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
+      <c r="I127" s="13"/>
+      <c r="J127" s="13"/>
+      <c r="K127" s="13"/>
+      <c r="L127" s="13"/>
+      <c r="M127" s="13"/>
+      <c r="N127" s="13"/>
+      <c r="O127" s="13"/>
+      <c r="P127" s="13"/>
+      <c r="Q127" s="13"/>
+      <c r="R127" s="13"/>
+      <c r="S127" s="13"/>
+      <c r="T127" s="13"/>
+      <c r="U127" s="13"/>
+      <c r="V127" s="13"/>
+      <c r="W127" s="13"/>
+    </row>
+    <row r="128" spans="1:24">
+      <c r="A128" t="s">
+        <v>93</v>
+      </c>
+      <c r="B128">
+        <v>3.5</v>
+      </c>
+      <c r="E128" t="s">
+        <v>13</v>
+      </c>
+      <c r="G128" t="s">
+        <v>13</v>
+      </c>
+      <c r="I128" t="s">
+        <v>13</v>
+      </c>
+      <c r="K128" t="s">
+        <v>14</v>
+      </c>
+      <c r="M128" t="s">
+        <v>13</v>
+      </c>
+      <c r="O128" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>13</v>
+      </c>
+      <c r="S128" t="s">
+        <v>13</v>
+      </c>
+      <c r="U128" t="s">
+        <v>13</v>
+      </c>
+      <c r="W128" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24">
+      <c r="A129" t="s">
+        <v>93</v>
+      </c>
+      <c r="B129">
+        <v>2.5</v>
+      </c>
+      <c r="E129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>14</v>
+      </c>
+      <c r="I129" t="s">
+        <v>14</v>
+      </c>
+      <c r="K129" t="s">
+        <v>14</v>
+      </c>
+      <c r="M129" t="s">
+        <v>14</v>
+      </c>
+      <c r="O129" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>14</v>
+      </c>
+      <c r="S129" t="s">
+        <v>14</v>
+      </c>
+      <c r="U129" t="s">
+        <v>13</v>
+      </c>
+      <c r="W129" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24">
+      <c r="C131" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D131" s="5"/>
+      <c r="E131" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F131" s="5"/>
+      <c r="G131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H131" s="5"/>
+      <c r="I131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J131" s="5"/>
+      <c r="K131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L131" s="5"/>
+      <c r="M131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N131" s="5"/>
+      <c r="O131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P131" s="5"/>
+      <c r="Q131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R131" s="5"/>
+      <c r="S131" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T131" s="5"/>
+      <c r="U131" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V131" s="5"/>
+      <c r="W131" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24">
+      <c r="C132" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="5"/>
+      <c r="E132" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F132" s="5"/>
+      <c r="G132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="H132" s="5"/>
+      <c r="I132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="J132" s="5"/>
+      <c r="K132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="L132" s="5"/>
+      <c r="M132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="N132" s="5"/>
+      <c r="O132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="P132" s="5"/>
+      <c r="Q132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="R132" s="5"/>
+      <c r="S132" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="T132" s="5"/>
+      <c r="U132" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="V132" s="5"/>
+      <c r="W132" s="6">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24">
+      <c r="C133" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D133" s="5"/>
+      <c r="E133" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F133" s="5"/>
+      <c r="G133" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="H133" s="5"/>
+      <c r="I133" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J133" s="5"/>
+      <c r="K133" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L133" s="5"/>
+      <c r="M133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="N133" s="5"/>
+      <c r="O133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P133" s="5"/>
+      <c r="Q133" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="R133" s="5"/>
+      <c r="S133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T133" s="5"/>
+      <c r="U133" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="V133" s="5"/>
+      <c r="W133" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24">
+      <c r="C134" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D134" s="5"/>
+      <c r="E134" s="5">
+        <v>-130</v>
+      </c>
+      <c r="F134" s="5"/>
+      <c r="G134" s="5">
+        <v>-150</v>
+      </c>
+      <c r="H134" s="5"/>
+      <c r="I134" s="5">
+        <v>-340</v>
+      </c>
+      <c r="J134" s="5"/>
+      <c r="K134" s="5">
+        <v>-310</v>
+      </c>
+      <c r="L134" s="5"/>
+      <c r="M134" s="5">
+        <v>-285</v>
+      </c>
+      <c r="N134" s="5"/>
+      <c r="O134" s="5">
+        <v>-240</v>
+      </c>
+      <c r="P134" s="5"/>
+      <c r="Q134" s="5">
+        <v>-295</v>
+      </c>
+      <c r="R134" s="5"/>
+      <c r="S134" s="5">
+        <v>-275</v>
+      </c>
+      <c r="T134" s="5"/>
+      <c r="U134" s="5">
+        <v>135</v>
+      </c>
+      <c r="V134" s="5"/>
+      <c r="W134" s="6">
+        <v>-330</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24">
+      <c r="C136" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D136" s="5"/>
+      <c r="E136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F136" s="5"/>
+      <c r="G136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H136" s="5"/>
+      <c r="I136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="J136" s="5"/>
+      <c r="K136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="L136" s="5"/>
+      <c r="M136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="N136" s="5"/>
+      <c r="O136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P136" s="5"/>
+      <c r="Q136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R136" s="5"/>
+      <c r="S136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T136" s="5"/>
+      <c r="U136" s="5">
+        <v>-1</v>
+      </c>
+      <c r="V136" s="5"/>
+      <c r="W136" s="6">
+        <v>-1</v>
+      </c>
+      <c r="X136" s="8">
+        <f>SUM(E136:W136)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24">
+      <c r="C137" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="5"/>
+      <c r="E137" s="5">
+        <v>0.76</v>
+      </c>
+      <c r="F137" s="5"/>
+      <c r="G137" s="5">
+        <f>IF(G134&gt;0,ROUND(ABS(G136)*(G134/100),2),ROUND(G136/(G134/100),2))</f>
+        <v>0.67</v>
+      </c>
+      <c r="H137" s="5"/>
+      <c r="I137" s="5">
+        <f>IF(I134&gt;0,ROUND(ABS(I136)*(I134/100),2),ROUND(I136/(I134/100),2))</f>
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J137" s="5"/>
+      <c r="K137" s="5">
+        <f>IF(K134&gt;0,ROUND(ABS(K136)*(K134/100),2),ROUND(K136/(K134/100),2))</f>
+        <v>0.32</v>
+      </c>
+      <c r="L137" s="5"/>
+      <c r="M137" s="5">
+        <f>IF(M134&gt;0,ROUND(ABS(M136)*(M134/100),2),ROUND(M136/(M134/100),2))</f>
+        <v>0.35</v>
+      </c>
+      <c r="N137" s="5"/>
+      <c r="O137" s="5">
+        <v>0.41</v>
+      </c>
+      <c r="P137" s="5"/>
+      <c r="Q137" s="5">
+        <v>0.33</v>
+      </c>
+      <c r="R137" s="5"/>
+      <c r="S137" s="5">
+        <f>IF(S134&gt;0,ROUND(ABS(S136)*(S134/100),2),ROUND(S136/(S134/100),2))</f>
+        <v>0.36</v>
+      </c>
+      <c r="T137" s="5"/>
+      <c r="U137" s="5">
+        <f>IF(U134&gt;0,ROUND(ABS(U136)*(U134/100),2),ROUND(U136/(U134/100),2))</f>
+        <v>1.35</v>
+      </c>
+      <c r="V137" s="5"/>
+      <c r="W137" s="5">
+        <f>IF(W134&gt;0,ROUND(ABS(W136)*(W134/100),2),ROUND(W136/(W134/100),2))</f>
+        <v>0.3</v>
+      </c>
+      <c r="X137" s="8">
+        <f>SUM(E137:W137)</f>
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24">
+      <c r="C138" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D138" s="5"/>
+      <c r="E138" s="5">
+        <f>IF(E133=E131,-E136+E137,0)</f>
+        <v>1.76</v>
+      </c>
+      <c r="F138" s="5"/>
+      <c r="G138" s="5">
+        <f>IF(G133=G131,-G136+G137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H138" s="5"/>
+      <c r="I138" s="5">
+        <f>IF(I133=I131,-I136+I137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J138" s="5"/>
+      <c r="K138" s="5">
+        <f>IF(K133=K131,-K136+K137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L138" s="5"/>
+      <c r="M138" s="5">
+        <f>IF(M133=M131,-M136+M137,0)</f>
+        <v>1.35</v>
+      </c>
+      <c r="N138" s="5"/>
+      <c r="O138" s="5">
+        <f>IF(O133=O131,-O136+O137,0)</f>
+        <v>1.41</v>
+      </c>
+      <c r="P138" s="5"/>
+      <c r="Q138" s="5">
+        <f>IF(Q133=Q131,-Q136+Q137,0)</f>
+        <v>1.33</v>
+      </c>
+      <c r="R138" s="5"/>
+      <c r="S138" s="5">
+        <f>IF(S133=S131,-S136+S137,0)</f>
+        <v>1.3599999999999999</v>
+      </c>
+      <c r="T138" s="5"/>
+      <c r="U138" s="5">
+        <f>IF(U133=U131,-U136+U137,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V138" s="5"/>
+      <c r="W138" s="6">
+        <f>IF(W133=W131,-W136+W137,0)</f>
+        <v>1.3</v>
+      </c>
+      <c r="X138" s="9">
+        <f>SUM(E138:W138)</f>
+        <v>8.5100000000000016</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24">
+      <c r="X139" s="7">
+        <f>X136+X138</f>
+        <v>-1.4899999999999984</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24">
+      <c r="V140" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="W140" s="13"/>
+      <c r="X140" s="11">
+        <f>X121+X139</f>
+        <v>-0.87999999999999901</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" ht="24">
+      <c r="E141" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="F141" s="12"/>
+      <c r="G141" s="12"/>
+      <c r="H141" s="12"/>
+      <c r="I141" s="12"/>
+      <c r="J141" s="12"/>
+      <c r="K141" s="12"/>
+      <c r="L141" s="12"/>
+      <c r="M141" s="12"/>
+      <c r="N141" s="12"/>
+      <c r="O141" s="12"/>
+      <c r="P141" s="12"/>
+      <c r="Q141" s="12"/>
+      <c r="R141" s="12"/>
+      <c r="S141" s="12"/>
+      <c r="T141" s="12"/>
+      <c r="U141" s="12"/>
+      <c r="V141" s="12"/>
+      <c r="W141" s="12"/>
+    </row>
+    <row r="142" spans="1:24">
+      <c r="A142" t="s">
+        <v>80</v>
+      </c>
+      <c r="E142" t="s">
+        <v>107</v>
+      </c>
+      <c r="G142" t="s">
+        <v>108</v>
+      </c>
+      <c r="I142" t="s">
+        <v>109</v>
+      </c>
+      <c r="K142" t="s">
+        <v>110</v>
+      </c>
+      <c r="M142" t="s">
+        <v>111</v>
+      </c>
+      <c r="O142" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>113</v>
+      </c>
+      <c r="S142" t="s">
+        <v>114</v>
+      </c>
+      <c r="U142" t="s">
+        <v>115</v>
+      </c>
+      <c r="W142" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24">
+      <c r="A143" t="s">
+        <v>91</v>
+      </c>
+      <c r="B143">
+        <v>3.5</v>
+      </c>
+      <c r="C143" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E143" t="s">
+        <v>13</v>
+      </c>
+      <c r="G143" t="s">
+        <v>13</v>
+      </c>
+      <c r="I143" t="s">
+        <v>13</v>
+      </c>
+      <c r="K143" t="s">
+        <v>13</v>
+      </c>
+      <c r="M143" t="s">
+        <v>13</v>
+      </c>
+      <c r="O143" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>13</v>
+      </c>
+      <c r="S143" t="s">
+        <v>13</v>
+      </c>
+      <c r="U143" t="s">
+        <v>13</v>
+      </c>
+      <c r="W143" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24">
+      <c r="A144" t="s">
+        <v>91</v>
+      </c>
+      <c r="B144">
+        <v>2.5</v>
+      </c>
+      <c r="C144" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E144" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" t="s">
+        <v>13</v>
+      </c>
+      <c r="I144" t="s">
+        <v>13</v>
+      </c>
+      <c r="K144" t="s">
+        <v>13</v>
+      </c>
+      <c r="M144" t="s">
+        <v>13</v>
+      </c>
+      <c r="O144" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>13</v>
+      </c>
+      <c r="S144" t="s">
+        <v>13</v>
+      </c>
+      <c r="U144" t="s">
+        <v>13</v>
+      </c>
+      <c r="W144" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24">
+      <c r="A145" t="s">
+        <v>91</v>
+      </c>
+      <c r="B145">
+        <v>3.5</v>
+      </c>
+      <c r="C145" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E145" t="s">
+        <v>13</v>
+      </c>
+      <c r="G145" t="s">
+        <v>13</v>
+      </c>
+      <c r="I145" t="s">
+        <v>13</v>
+      </c>
+      <c r="K145" t="s">
+        <v>13</v>
+      </c>
+      <c r="M145" t="s">
+        <v>13</v>
+      </c>
+      <c r="O145" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>13</v>
+      </c>
+      <c r="S145" t="s">
+        <v>13</v>
+      </c>
+      <c r="U145" t="s">
+        <v>13</v>
+      </c>
+      <c r="W145" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24">
+      <c r="A146" t="s">
+        <v>91</v>
+      </c>
+      <c r="B146">
+        <v>2.5</v>
+      </c>
+      <c r="C146" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E146" t="s">
+        <v>13</v>
+      </c>
+      <c r="G146" t="s">
+        <v>13</v>
+      </c>
+      <c r="I146" t="s">
+        <v>13</v>
+      </c>
+      <c r="K146" t="s">
+        <v>13</v>
+      </c>
+      <c r="M146" t="s">
+        <v>13</v>
+      </c>
+      <c r="O146" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q146" t="s">
+        <v>13</v>
+      </c>
+      <c r="S146" t="s">
+        <v>13</v>
+      </c>
+      <c r="U146" t="s">
+        <v>13</v>
+      </c>
+      <c r="W146" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24">
+      <c r="A147" t="s">
+        <v>93</v>
+      </c>
+      <c r="B147">
+        <v>3.5</v>
+      </c>
+      <c r="E147" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" t="s">
+        <v>13</v>
+      </c>
+      <c r="I147" t="s">
+        <v>13</v>
+      </c>
+      <c r="K147" t="s">
+        <v>14</v>
+      </c>
+      <c r="M147" t="s">
+        <v>13</v>
+      </c>
+      <c r="O147" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>13</v>
+      </c>
+      <c r="S147" t="s">
+        <v>13</v>
+      </c>
+      <c r="U147" t="s">
+        <v>13</v>
+      </c>
+      <c r="W147" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24">
+      <c r="A148" t="s">
+        <v>93</v>
+      </c>
+      <c r="B148">
+        <v>2.5</v>
+      </c>
+      <c r="E148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" t="s">
+        <v>13</v>
+      </c>
+      <c r="I148" t="s">
+        <v>14</v>
+      </c>
+      <c r="K148" t="s">
+        <v>14</v>
+      </c>
+      <c r="M148" t="s">
+        <v>14</v>
+      </c>
+      <c r="O148" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>14</v>
+      </c>
+      <c r="S148" t="s">
+        <v>13</v>
+      </c>
+      <c r="U148" t="s">
+        <v>14</v>
+      </c>
+      <c r="W148" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24">
+      <c r="C150" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D150" s="5"/>
+      <c r="E150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="F150" s="5"/>
+      <c r="G150" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H150" s="5"/>
+      <c r="I150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="J150" s="5"/>
+      <c r="K150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="L150" s="5"/>
+      <c r="M150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N150" s="5"/>
+      <c r="O150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="P150" s="5"/>
+      <c r="Q150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="R150" s="5"/>
+      <c r="S150" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T150" s="5"/>
+      <c r="U150" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="V150" s="5"/>
+      <c r="W150" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24">
+      <c r="C151" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D151" s="5"/>
+      <c r="E151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F151" s="5"/>
+      <c r="G151" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="H151" s="5"/>
+      <c r="I151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="J151" s="5"/>
+      <c r="K151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="L151" s="5"/>
+      <c r="M151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="N151" s="5"/>
+      <c r="O151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="P151" s="5"/>
+      <c r="Q151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="R151" s="5"/>
+      <c r="S151" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="T151" s="5"/>
+      <c r="U151" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="V151" s="5"/>
+      <c r="W151" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24">
+      <c r="C152" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D152" s="5"/>
+      <c r="E152" s="5"/>
+      <c r="F152" s="5"/>
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+      <c r="I152" s="5"/>
+      <c r="J152" s="5"/>
+      <c r="K152" s="5"/>
+      <c r="L152" s="5"/>
+      <c r="M152" s="5"/>
+      <c r="N152" s="5"/>
+      <c r="O152" s="5"/>
+      <c r="P152" s="5"/>
+      <c r="Q152" s="5"/>
+      <c r="R152" s="5"/>
+      <c r="S152" s="5"/>
+      <c r="T152" s="5"/>
+      <c r="U152" s="5"/>
+      <c r="V152" s="5"/>
+      <c r="W152" s="6"/>
+    </row>
+    <row r="153" spans="1:24">
+      <c r="C153" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D153" s="5"/>
+      <c r="E153" s="5">
+        <v>-150</v>
+      </c>
+      <c r="F153" s="5"/>
+      <c r="G153" s="5">
+        <v>-310</v>
+      </c>
+      <c r="H153" s="5"/>
+      <c r="I153" s="5">
+        <v>-160</v>
+      </c>
+      <c r="J153" s="5"/>
+      <c r="K153" s="5">
+        <v>-135</v>
+      </c>
+      <c r="L153" s="5"/>
+      <c r="M153" s="5">
+        <v>-120</v>
+      </c>
+      <c r="N153" s="5"/>
+      <c r="O153" s="5">
+        <v>105</v>
+      </c>
+      <c r="P153" s="5"/>
+      <c r="Q153" s="5">
+        <v>100</v>
+      </c>
+      <c r="R153" s="5"/>
+      <c r="S153" s="5">
+        <v>-180</v>
+      </c>
+      <c r="T153" s="5"/>
+      <c r="U153" s="5">
+        <v>-120</v>
+      </c>
+      <c r="V153" s="5"/>
+      <c r="W153" s="6">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24">
+      <c r="C155" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D155" s="5"/>
+      <c r="E155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F155" s="5"/>
+      <c r="G155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H155" s="5"/>
+      <c r="I155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="J155" s="5"/>
+      <c r="K155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="L155" s="5"/>
+      <c r="M155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="N155" s="5"/>
+      <c r="O155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P155" s="5"/>
+      <c r="Q155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R155" s="5"/>
+      <c r="S155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T155" s="5"/>
+      <c r="U155" s="5">
+        <v>-1</v>
+      </c>
+      <c r="V155" s="5"/>
+      <c r="W155" s="6">
+        <v>-1</v>
+      </c>
+      <c r="X155" s="8">
+        <f>SUM(E155:W155)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24">
+      <c r="C156" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="5"/>
+      <c r="E156" s="5">
+        <f>IF(E153&gt;0,ROUND(ABS(E155)*(E153/100),2),ROUND(E155/(E153/100),2))</f>
+        <v>0.67</v>
+      </c>
+      <c r="F156" s="5"/>
+      <c r="G156" s="5">
+        <f>IF(G153&gt;0,ROUND(ABS(G155)*(G153/100),2),ROUND(G155/(G153/100),2))</f>
+        <v>0.32</v>
+      </c>
+      <c r="H156" s="5"/>
+      <c r="I156" s="5">
+        <f>IF(I153&gt;0,ROUND(ABS(I155)*(I153/100),2),ROUND(I155/(I153/100),2))</f>
+        <v>0.63</v>
+      </c>
+      <c r="J156" s="5"/>
+      <c r="K156" s="5">
+        <f>IF(K153&gt;0,ROUND(ABS(K155)*(K153/100),2),ROUND(K155/(K153/100),2))</f>
+        <v>0.74</v>
+      </c>
+      <c r="L156" s="5"/>
+      <c r="M156" s="5">
+        <f>IF(M153&gt;0,ROUND(ABS(M155)*(M153/100),2),ROUND(M155/(M153/100),2))</f>
+        <v>0.83</v>
+      </c>
+      <c r="N156" s="5"/>
+      <c r="O156" s="5">
+        <f>IF(O153&gt;0,ROUND(ABS(O155)*(O153/100),2),ROUND(O155/(O153/100),2))</f>
+        <v>1.05</v>
+      </c>
+      <c r="P156" s="5"/>
+      <c r="Q156" s="5">
+        <f>IF(Q153&gt;0,ROUND(ABS(Q155)*(Q153/100),2),ROUND(Q155/(Q153/100),2))</f>
+        <v>1</v>
+      </c>
+      <c r="R156" s="5"/>
+      <c r="S156" s="5">
+        <f>IF(S153&gt;0,ROUND(ABS(S155)*(S153/100),2),ROUND(S155/(S153/100),2))</f>
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="T156" s="5"/>
+      <c r="U156" s="5">
+        <f>IF(U153&gt;0,ROUND(ABS(U155)*(U153/100),2),ROUND(U155/(U153/100),2))</f>
+        <v>0.83</v>
+      </c>
+      <c r="V156" s="5"/>
+      <c r="W156" s="5">
+        <f>IF(W153&gt;0,ROUND(ABS(W155)*(W153/100),2),ROUND(W155/(W153/100),2))</f>
+        <v>0.5</v>
+      </c>
+      <c r="X156" s="8">
+        <f>SUM(E156:W156)</f>
+        <v>7.1300000000000008</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24">
+      <c r="C157" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D157" s="5"/>
+      <c r="E157" s="5">
+        <f>IF(E152=E150,-E155+E156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F157" s="5"/>
+      <c r="G157" s="5">
+        <f>IF(G152=G150,-G155+G156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H157" s="5"/>
+      <c r="I157" s="5">
+        <f>IF(I152=I150,-I155+I156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J157" s="5"/>
+      <c r="K157" s="5">
+        <f>IF(K152=K150,-K155+K156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L157" s="5"/>
+      <c r="M157" s="5">
+        <f>IF(M152=M150,-M155+M156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N157" s="5"/>
+      <c r="O157" s="5">
+        <f>IF(O152=O150,-O155+O156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P157" s="5"/>
+      <c r="Q157" s="5">
+        <f>IF(Q152=Q150,-Q155+Q156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R157" s="5"/>
+      <c r="S157" s="5">
+        <f>IF(S152=S150,-S155+S156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T157" s="5"/>
+      <c r="U157" s="5">
+        <f>IF(U152=U150,-U155+U156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V157" s="5"/>
+      <c r="W157" s="6">
+        <f>IF(W152=W150,-W155+W156,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X157" s="9">
+        <f>SUM(E157:W157)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24">
+      <c r="X158" s="7">
+        <f>X155+X157</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24">
+      <c r="V159" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="W159" s="13"/>
+      <c r="X159" s="11">
+        <f>X140+X158</f>
+        <v>-10.879999999999999</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="21">
+    <mergeCell ref="Y105:Z110"/>
+    <mergeCell ref="E122:W122"/>
+    <mergeCell ref="V140:W140"/>
     <mergeCell ref="E103:W103"/>
     <mergeCell ref="V121:W121"/>
-    <mergeCell ref="V51:W51"/>
     <mergeCell ref="E1:W1"/>
     <mergeCell ref="E18:W18"/>
     <mergeCell ref="E35:W35"/>
     <mergeCell ref="V17:W17"/>
     <mergeCell ref="V34:W34"/>
-    <mergeCell ref="E86:W86"/>
-    <mergeCell ref="V102:W102"/>
     <mergeCell ref="E69:W69"/>
     <mergeCell ref="V85:W85"/>
     <mergeCell ref="E52:W52"/>
     <mergeCell ref="V68:W68"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="E141:W141"/>
+    <mergeCell ref="V159:W159"/>
+    <mergeCell ref="E125:W125"/>
+    <mergeCell ref="E127:W127"/>
+    <mergeCell ref="E86:W86"/>
+    <mergeCell ref="V102:W102"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Predictions 2(Records).xlsx
+++ b/Predictions 2(Records).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29523"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mattc\git-folder\Premier-League-Predictions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C19D062F-42CC-4F98-8CCF-C1C4DB6DEA38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E0E9FFC-0161-46FC-8BB5-59AABEC0E142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B97D2B54-78E2-448B-A9CF-77B7E3BC2EA1}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="130">
   <si>
     <t>Goals</t>
   </si>
@@ -356,6 +356,9 @@
     <t>Did Not Calculate</t>
   </si>
   <si>
+    <t>Games Correct (XG Boost)</t>
+  </si>
+  <si>
     <t>Match Week 14 - Started using XGBoost for bets</t>
   </si>
   <si>
@@ -387,6 +390,42 @@
   </si>
   <si>
     <t>MUN vs WHU</t>
+  </si>
+  <si>
+    <t>Using This One</t>
+  </si>
+  <si>
+    <t>Match Week 15</t>
+  </si>
+  <si>
+    <t>AVL vs ARS</t>
+  </si>
+  <si>
+    <t>BOU vs CHE</t>
+  </si>
+  <si>
+    <t>EVE vs NOF</t>
+  </si>
+  <si>
+    <t>MCI vs SUN</t>
+  </si>
+  <si>
+    <t>TOT vs BRE</t>
+  </si>
+  <si>
+    <t>NCU vs BUR</t>
+  </si>
+  <si>
+    <t>LEE vs LIV</t>
+  </si>
+  <si>
+    <t>BHA vs WHU</t>
+  </si>
+  <si>
+    <t>FUL vs CRY</t>
+  </si>
+  <si>
+    <t>WOL vs MUN</t>
   </si>
 </sst>
 </file>
@@ -1014,14 +1053,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1398,7 +1437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA341253-1EAB-4104-BE4B-374BC158237A}">
-  <dimension ref="A1:Z159"/>
+  <dimension ref="A1:Z178"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="5" max="5" width="10.7109375" bestFit="1" customWidth="1"/>
@@ -1408,27 +1447,27 @@
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
     </row>
     <row r="2" spans="2:24">
       <c r="E2" t="s">
@@ -1828,37 +1867,37 @@
       </c>
     </row>
     <row r="17" spans="2:24" ht="15.75" thickBot="1">
-      <c r="V17" s="13" t="s">
+      <c r="V17" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W17" s="13"/>
+      <c r="W17" s="14"/>
       <c r="X17" s="11">
         <f>X16</f>
         <v>-0.74000000000000021</v>
       </c>
     </row>
     <row r="18" spans="2:24" ht="24">
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="13"/>
+      <c r="M18" s="13"/>
+      <c r="N18" s="13"/>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13"/>
+      <c r="Q18" s="13"/>
+      <c r="R18" s="13"/>
+      <c r="S18" s="13"/>
+      <c r="T18" s="13"/>
+      <c r="U18" s="13"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
     </row>
     <row r="19" spans="2:24">
       <c r="E19" t="s">
@@ -2298,37 +2337,37 @@
       </c>
     </row>
     <row r="34" spans="2:24" ht="15.75" thickBot="1">
-      <c r="V34" s="13" t="s">
+      <c r="V34" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W34" s="13"/>
+      <c r="W34" s="14"/>
       <c r="X34" s="11">
         <f>X33+X17</f>
         <v>-0.58000000000000007</v>
       </c>
     </row>
     <row r="35" spans="2:24" ht="24">
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
-      <c r="K35" s="12"/>
-      <c r="L35" s="12"/>
-      <c r="M35" s="12"/>
-      <c r="N35" s="12"/>
-      <c r="O35" s="12"/>
-      <c r="P35" s="12"/>
-      <c r="Q35" s="12"/>
-      <c r="R35" s="12"/>
-      <c r="S35" s="12"/>
-      <c r="T35" s="12"/>
-      <c r="U35" s="12"/>
-      <c r="V35" s="12"/>
-      <c r="W35" s="12"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
     </row>
     <row r="36" spans="2:24">
       <c r="E36" t="s">
@@ -2854,37 +2893,37 @@
       </c>
     </row>
     <row r="51" spans="2:24" ht="15.75" thickBot="1">
-      <c r="V51" s="13" t="s">
+      <c r="V51" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W51" s="13"/>
+      <c r="W51" s="14"/>
       <c r="X51" s="11">
         <f>X34+X50</f>
         <v>0.82000000000000028</v>
       </c>
     </row>
     <row r="52" spans="2:24" ht="24">
-      <c r="E52" s="12" t="s">
+      <c r="E52" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12"/>
-      <c r="J52" s="12"/>
-      <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
-      <c r="M52" s="12"/>
-      <c r="N52" s="12"/>
-      <c r="O52" s="12"/>
-      <c r="P52" s="12"/>
-      <c r="Q52" s="12"/>
-      <c r="R52" s="12"/>
-      <c r="S52" s="12"/>
-      <c r="T52" s="12"/>
-      <c r="U52" s="12"/>
-      <c r="V52" s="12"/>
-      <c r="W52" s="12"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
+      <c r="I52" s="13"/>
+      <c r="J52" s="13"/>
+      <c r="K52" s="13"/>
+      <c r="L52" s="13"/>
+      <c r="M52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13"/>
+      <c r="P52" s="13"/>
+      <c r="Q52" s="13"/>
+      <c r="R52" s="13"/>
+      <c r="S52" s="13"/>
+      <c r="T52" s="13"/>
+      <c r="U52" s="13"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="13"/>
     </row>
     <row r="53" spans="2:24">
       <c r="E53" t="s">
@@ -3424,37 +3463,37 @@
       </c>
     </row>
     <row r="68" spans="2:24" ht="15.75" thickBot="1">
-      <c r="V68" s="13" t="s">
+      <c r="V68" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W68" s="13"/>
+      <c r="W68" s="14"/>
       <c r="X68" s="11">
         <f>X51+X67</f>
         <v>1.0899999999999999</v>
       </c>
     </row>
     <row r="69" spans="2:24" ht="24">
-      <c r="E69" s="12" t="s">
+      <c r="E69" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="F69" s="12"/>
-      <c r="G69" s="12"/>
-      <c r="H69" s="12"/>
-      <c r="I69" s="12"/>
-      <c r="J69" s="12"/>
-      <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
-      <c r="M69" s="12"/>
-      <c r="N69" s="12"/>
-      <c r="O69" s="12"/>
-      <c r="P69" s="12"/>
-      <c r="Q69" s="12"/>
-      <c r="R69" s="12"/>
-      <c r="S69" s="12"/>
-      <c r="T69" s="12"/>
-      <c r="U69" s="12"/>
-      <c r="V69" s="12"/>
-      <c r="W69" s="12"/>
+      <c r="F69" s="13"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
+      <c r="I69" s="13"/>
+      <c r="J69" s="13"/>
+      <c r="K69" s="13"/>
+      <c r="L69" s="13"/>
+      <c r="M69" s="13"/>
+      <c r="N69" s="13"/>
+      <c r="O69" s="13"/>
+      <c r="P69" s="13"/>
+      <c r="Q69" s="13"/>
+      <c r="R69" s="13"/>
+      <c r="S69" s="13"/>
+      <c r="T69" s="13"/>
+      <c r="U69" s="13"/>
+      <c r="V69" s="13"/>
+      <c r="W69" s="13"/>
     </row>
     <row r="70" spans="2:24">
       <c r="E70" t="s">
@@ -3994,37 +4033,37 @@
       </c>
     </row>
     <row r="85" spans="2:24" ht="15.75" thickBot="1">
-      <c r="V85" s="13" t="s">
+      <c r="V85" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W85" s="13"/>
+      <c r="W85" s="14"/>
       <c r="X85" s="11">
         <f>X68+X84</f>
         <v>1.3200000000000003</v>
       </c>
     </row>
     <row r="86" spans="2:24" ht="24">
-      <c r="E86" s="12" t="s">
+      <c r="E86" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="F86" s="12"/>
-      <c r="G86" s="12"/>
-      <c r="H86" s="12"/>
-      <c r="I86" s="12"/>
-      <c r="J86" s="12"/>
-      <c r="K86" s="12"/>
-      <c r="L86" s="12"/>
-      <c r="M86" s="12"/>
-      <c r="N86" s="12"/>
-      <c r="O86" s="12"/>
-      <c r="P86" s="12"/>
-      <c r="Q86" s="12"/>
-      <c r="R86" s="12"/>
-      <c r="S86" s="12"/>
-      <c r="T86" s="12"/>
-      <c r="U86" s="12"/>
-      <c r="V86" s="12"/>
-      <c r="W86" s="12"/>
+      <c r="F86" s="13"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
+      <c r="I86" s="13"/>
+      <c r="J86" s="13"/>
+      <c r="K86" s="13"/>
+      <c r="L86" s="13"/>
+      <c r="M86" s="13"/>
+      <c r="N86" s="13"/>
+      <c r="O86" s="13"/>
+      <c r="P86" s="13"/>
+      <c r="Q86" s="13"/>
+      <c r="R86" s="13"/>
+      <c r="S86" s="13"/>
+      <c r="T86" s="13"/>
+      <c r="U86" s="13"/>
+      <c r="V86" s="13"/>
+      <c r="W86" s="13"/>
     </row>
     <row r="87" spans="2:24">
       <c r="E87" t="s">
@@ -4564,37 +4603,37 @@
       </c>
     </row>
     <row r="102" spans="1:26" ht="15.75" thickBot="1">
-      <c r="V102" s="13" t="s">
+      <c r="V102" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W102" s="13"/>
+      <c r="W102" s="14"/>
       <c r="X102" s="11">
         <f>X85+X101</f>
         <v>-2.3100000000000005</v>
       </c>
     </row>
     <row r="103" spans="1:26" ht="24">
-      <c r="E103" s="12" t="s">
+      <c r="E103" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="F103" s="12"/>
-      <c r="G103" s="12"/>
-      <c r="H103" s="12"/>
-      <c r="I103" s="12"/>
-      <c r="J103" s="12"/>
-      <c r="K103" s="12"/>
-      <c r="L103" s="12"/>
-      <c r="M103" s="12"/>
-      <c r="N103" s="12"/>
-      <c r="O103" s="12"/>
-      <c r="P103" s="12"/>
-      <c r="Q103" s="12"/>
-      <c r="R103" s="12"/>
-      <c r="S103" s="12"/>
-      <c r="T103" s="12"/>
-      <c r="U103" s="12"/>
-      <c r="V103" s="12"/>
-      <c r="W103" s="12"/>
+      <c r="F103" s="13"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
+      <c r="I103" s="13"/>
+      <c r="J103" s="13"/>
+      <c r="K103" s="13"/>
+      <c r="L103" s="13"/>
+      <c r="M103" s="13"/>
+      <c r="N103" s="13"/>
+      <c r="O103" s="13"/>
+      <c r="P103" s="13"/>
+      <c r="Q103" s="13"/>
+      <c r="R103" s="13"/>
+      <c r="S103" s="13"/>
+      <c r="T103" s="13"/>
+      <c r="U103" s="13"/>
+      <c r="V103" s="13"/>
+      <c r="W103" s="13"/>
     </row>
     <row r="104" spans="1:26">
       <c r="A104" t="s">
@@ -4671,10 +4710,10 @@
       <c r="W105" t="s">
         <v>13</v>
       </c>
-      <c r="Y105" s="14" t="s">
+      <c r="Y105" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="Z105" s="14"/>
+      <c r="Z105" s="12"/>
     </row>
     <row r="106" spans="1:26">
       <c r="A106" t="s">
@@ -4716,8 +4755,8 @@
       <c r="W106" t="s">
         <v>13</v>
       </c>
-      <c r="Y106" s="14"/>
-      <c r="Z106" s="14"/>
+      <c r="Y106" s="12"/>
+      <c r="Z106" s="12"/>
     </row>
     <row r="107" spans="1:26">
       <c r="A107" t="s">
@@ -4759,8 +4798,8 @@
       <c r="W107" t="s">
         <v>13</v>
       </c>
-      <c r="Y107" s="14"/>
-      <c r="Z107" s="14"/>
+      <c r="Y107" s="12"/>
+      <c r="Z107" s="12"/>
     </row>
     <row r="108" spans="1:26">
       <c r="A108" t="s">
@@ -4802,8 +4841,8 @@
       <c r="W108" t="s">
         <v>14</v>
       </c>
-      <c r="Y108" s="14"/>
-      <c r="Z108" s="14"/>
+      <c r="Y108" s="12"/>
+      <c r="Z108" s="12"/>
     </row>
     <row r="109" spans="1:26">
       <c r="A109" t="s">
@@ -4842,8 +4881,8 @@
       <c r="W109" t="s">
         <v>13</v>
       </c>
-      <c r="Y109" s="14"/>
-      <c r="Z109" s="14"/>
+      <c r="Y109" s="12"/>
+      <c r="Z109" s="12"/>
     </row>
     <row r="110" spans="1:26">
       <c r="A110" t="s">
@@ -4882,8 +4921,8 @@
       <c r="W110" t="s">
         <v>13</v>
       </c>
-      <c r="Y110" s="14"/>
-      <c r="Z110" s="14"/>
+      <c r="Y110" s="12"/>
+      <c r="Z110" s="12"/>
     </row>
     <row r="112" spans="1:26">
       <c r="C112" s="4" t="s">
@@ -5235,37 +5274,37 @@
       </c>
     </row>
     <row r="121" spans="1:24">
-      <c r="V121" s="13" t="s">
+      <c r="V121" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W121" s="13"/>
+      <c r="W121" s="14"/>
       <c r="X121" s="11">
         <f>X102+X120</f>
         <v>0.60999999999999943</v>
       </c>
     </row>
     <row r="122" spans="1:24" ht="24">
-      <c r="E122" s="12" t="s">
+      <c r="E122" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F122" s="12"/>
-      <c r="G122" s="12"/>
-      <c r="H122" s="12"/>
-      <c r="I122" s="12"/>
-      <c r="J122" s="12"/>
-      <c r="K122" s="12"/>
-      <c r="L122" s="12"/>
-      <c r="M122" s="12"/>
-      <c r="N122" s="12"/>
-      <c r="O122" s="12"/>
-      <c r="P122" s="12"/>
-      <c r="Q122" s="12"/>
-      <c r="R122" s="12"/>
-      <c r="S122" s="12"/>
-      <c r="T122" s="12"/>
-      <c r="U122" s="12"/>
-      <c r="V122" s="12"/>
-      <c r="W122" s="12"/>
+      <c r="F122" s="13"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
+      <c r="I122" s="13"/>
+      <c r="J122" s="13"/>
+      <c r="K122" s="13"/>
+      <c r="L122" s="13"/>
+      <c r="M122" s="13"/>
+      <c r="N122" s="13"/>
+      <c r="O122" s="13"/>
+      <c r="P122" s="13"/>
+      <c r="Q122" s="13"/>
+      <c r="R122" s="13"/>
+      <c r="S122" s="13"/>
+      <c r="T122" s="13"/>
+      <c r="U122" s="13"/>
+      <c r="V122" s="13"/>
+      <c r="W122" s="13"/>
     </row>
     <row r="123" spans="1:24">
       <c r="A123" t="s">
@@ -5353,27 +5392,27 @@
       <c r="C125" s="1">
         <v>0.8</v>
       </c>
-      <c r="E125" s="13" t="s">
+      <c r="E125" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F125" s="13"/>
-      <c r="G125" s="13"/>
-      <c r="H125" s="13"/>
-      <c r="I125" s="13"/>
-      <c r="J125" s="13"/>
-      <c r="K125" s="13"/>
-      <c r="L125" s="13"/>
-      <c r="M125" s="13"/>
-      <c r="N125" s="13"/>
-      <c r="O125" s="13"/>
-      <c r="P125" s="13"/>
-      <c r="Q125" s="13"/>
-      <c r="R125" s="13"/>
-      <c r="S125" s="13"/>
-      <c r="T125" s="13"/>
-      <c r="U125" s="13"/>
-      <c r="V125" s="13"/>
-      <c r="W125" s="13"/>
+      <c r="F125" s="14"/>
+      <c r="G125" s="14"/>
+      <c r="H125" s="14"/>
+      <c r="I125" s="14"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="14"/>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
+      <c r="N125" s="14"/>
+      <c r="O125" s="14"/>
+      <c r="P125" s="14"/>
+      <c r="Q125" s="14"/>
+      <c r="R125" s="14"/>
+      <c r="S125" s="14"/>
+      <c r="T125" s="14"/>
+      <c r="U125" s="14"/>
+      <c r="V125" s="14"/>
+      <c r="W125" s="14"/>
     </row>
     <row r="126" spans="1:24">
       <c r="A126" t="s">
@@ -5426,27 +5465,27 @@
       <c r="C127" s="1">
         <v>0.7</v>
       </c>
-      <c r="E127" s="13" t="s">
+      <c r="E127" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F127" s="13"/>
-      <c r="G127" s="13"/>
-      <c r="H127" s="13"/>
-      <c r="I127" s="13"/>
-      <c r="J127" s="13"/>
-      <c r="K127" s="13"/>
-      <c r="L127" s="13"/>
-      <c r="M127" s="13"/>
-      <c r="N127" s="13"/>
-      <c r="O127" s="13"/>
-      <c r="P127" s="13"/>
-      <c r="Q127" s="13"/>
-      <c r="R127" s="13"/>
-      <c r="S127" s="13"/>
-      <c r="T127" s="13"/>
-      <c r="U127" s="13"/>
-      <c r="V127" s="13"/>
-      <c r="W127" s="13"/>
+      <c r="F127" s="14"/>
+      <c r="G127" s="14"/>
+      <c r="H127" s="14"/>
+      <c r="I127" s="14"/>
+      <c r="J127" s="14"/>
+      <c r="K127" s="14"/>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
+      <c r="N127" s="14"/>
+      <c r="O127" s="14"/>
+      <c r="P127" s="14"/>
+      <c r="Q127" s="14"/>
+      <c r="R127" s="14"/>
+      <c r="S127" s="14"/>
+      <c r="T127" s="14"/>
+      <c r="U127" s="14"/>
+      <c r="V127" s="14"/>
+      <c r="W127" s="14"/>
     </row>
     <row r="128" spans="1:24">
       <c r="A128" t="s">
@@ -5486,7 +5525,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="129" spans="1:24">
+    <row r="129" spans="1:25">
       <c r="A129" t="s">
         <v>93</v>
       </c>
@@ -5524,7 +5563,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="131" spans="1:24">
+    <row r="131" spans="1:25">
       <c r="C131" s="4" t="s">
         <v>12</v>
       </c>
@@ -5569,7 +5608,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="132" spans="1:24">
+    <row r="132" spans="1:25">
       <c r="C132" s="4" t="s">
         <v>15</v>
       </c>
@@ -5614,7 +5653,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="133" spans="1:24">
+    <row r="133" spans="1:25">
       <c r="C133" s="4" t="s">
         <v>16</v>
       </c>
@@ -5659,7 +5698,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="134" spans="1:24">
+    <row r="134" spans="1:25">
       <c r="C134" s="4" t="s">
         <v>17</v>
       </c>
@@ -5704,7 +5743,48 @@
         <v>-330</v>
       </c>
     </row>
-    <row r="136" spans="1:24">
+    <row r="135" spans="1:25">
+      <c r="E135">
+        <f>IF(E131=E133,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G135">
+        <v>1</v>
+      </c>
+      <c r="I135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+      <c r="M135">
+        <v>1</v>
+      </c>
+      <c r="O135">
+        <f>IF(O131=O133,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q135">
+        <v>0</v>
+      </c>
+      <c r="S135">
+        <v>0</v>
+      </c>
+      <c r="U135">
+        <v>1</v>
+      </c>
+      <c r="W135">
+        <v>0</v>
+      </c>
+      <c r="X135">
+        <f>SUM(E135:W135)</f>
+        <v>7</v>
+      </c>
+      <c r="Y135" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="136" spans="1:25">
       <c r="C136" s="4" t="s">
         <v>18</v>
       </c>
@@ -5753,7 +5833,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="137" spans="1:24">
+    <row r="137" spans="1:25">
       <c r="C137" s="4" t="s">
         <v>19</v>
       </c>
@@ -5809,7 +5889,7 @@
         <v>5.14</v>
       </c>
     </row>
-    <row r="138" spans="1:24">
+    <row r="138" spans="1:25">
       <c r="C138" s="4" t="s">
         <v>20</v>
       </c>
@@ -5868,81 +5948,81 @@
         <v>8.5100000000000016</v>
       </c>
     </row>
-    <row r="139" spans="1:24">
+    <row r="139" spans="1:25">
       <c r="X139" s="7">
         <f>X136+X138</f>
         <v>-1.4899999999999984</v>
       </c>
     </row>
-    <row r="140" spans="1:24">
-      <c r="V140" s="13" t="s">
+    <row r="140" spans="1:25">
+      <c r="V140" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W140" s="13"/>
+      <c r="W140" s="14"/>
       <c r="X140" s="11">
         <f>X121+X139</f>
         <v>-0.87999999999999901</v>
       </c>
     </row>
-    <row r="141" spans="1:24" ht="24">
-      <c r="E141" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F141" s="12"/>
-      <c r="G141" s="12"/>
-      <c r="H141" s="12"/>
-      <c r="I141" s="12"/>
-      <c r="J141" s="12"/>
-      <c r="K141" s="12"/>
-      <c r="L141" s="12"/>
-      <c r="M141" s="12"/>
-      <c r="N141" s="12"/>
-      <c r="O141" s="12"/>
-      <c r="P141" s="12"/>
-      <c r="Q141" s="12"/>
-      <c r="R141" s="12"/>
-      <c r="S141" s="12"/>
-      <c r="T141" s="12"/>
-      <c r="U141" s="12"/>
-      <c r="V141" s="12"/>
-      <c r="W141" s="12"/>
-    </row>
-    <row r="142" spans="1:24">
+    <row r="141" spans="1:25" ht="24">
+      <c r="E141" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="F141" s="13"/>
+      <c r="G141" s="13"/>
+      <c r="H141" s="13"/>
+      <c r="I141" s="13"/>
+      <c r="J141" s="13"/>
+      <c r="K141" s="13"/>
+      <c r="L141" s="13"/>
+      <c r="M141" s="13"/>
+      <c r="N141" s="13"/>
+      <c r="O141" s="13"/>
+      <c r="P141" s="13"/>
+      <c r="Q141" s="13"/>
+      <c r="R141" s="13"/>
+      <c r="S141" s="13"/>
+      <c r="T141" s="13"/>
+      <c r="U141" s="13"/>
+      <c r="V141" s="13"/>
+      <c r="W141" s="13"/>
+    </row>
+    <row r="142" spans="1:25">
       <c r="A142" t="s">
         <v>80</v>
       </c>
       <c r="E142" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G142" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I142" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K142" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M142" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O142" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="Q142" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S142" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U142" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="W142" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="143" spans="1:24">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="143" spans="1:25">
       <c r="A143" t="s">
         <v>91</v>
       </c>
@@ -5983,7 +6063,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="144" spans="1:24">
+    <row r="144" spans="1:25">
       <c r="A144" t="s">
         <v>91</v>
       </c>
@@ -6024,7 +6104,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="145" spans="1:24">
+    <row r="145" spans="1:25">
       <c r="A145" t="s">
         <v>91</v>
       </c>
@@ -6065,7 +6145,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:24">
+    <row r="146" spans="1:25">
       <c r="A146" t="s">
         <v>91</v>
       </c>
@@ -6106,7 +6186,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="147" spans="1:24">
+    <row r="147" spans="1:25">
       <c r="A147" t="s">
         <v>93</v>
       </c>
@@ -6144,7 +6224,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="148" spans="1:24">
+    <row r="148" spans="1:25">
       <c r="A148" t="s">
         <v>93</v>
       </c>
@@ -6181,8 +6261,11 @@
       <c r="W148" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="150" spans="1:24">
+      <c r="X148" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="150" spans="1:25">
       <c r="C150" s="4" t="s">
         <v>12</v>
       </c>
@@ -6227,7 +6310,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="151" spans="1:24">
+    <row r="151" spans="1:25">
       <c r="C151" s="4" t="s">
         <v>15</v>
       </c>
@@ -6272,32 +6355,52 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="152" spans="1:24">
+    <row r="152" spans="1:25">
       <c r="C152" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D152" s="5"/>
-      <c r="E152" s="5"/>
+      <c r="E152" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="F152" s="5"/>
-      <c r="G152" s="5"/>
+      <c r="G152" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="H152" s="5"/>
-      <c r="I152" s="5"/>
+      <c r="I152" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="J152" s="5"/>
-      <c r="K152" s="5"/>
+      <c r="K152" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="L152" s="5"/>
-      <c r="M152" s="5"/>
+      <c r="M152" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="N152" s="5"/>
-      <c r="O152" s="5"/>
+      <c r="O152" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="P152" s="5"/>
-      <c r="Q152" s="5"/>
+      <c r="Q152" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="R152" s="5"/>
-      <c r="S152" s="5"/>
+      <c r="S152" s="5" t="s">
+        <v>13</v>
+      </c>
       <c r="T152" s="5"/>
-      <c r="U152" s="5"/>
+      <c r="U152" s="5" t="s">
+        <v>14</v>
+      </c>
       <c r="V152" s="5"/>
-      <c r="W152" s="6"/>
-    </row>
-    <row r="153" spans="1:24">
+      <c r="W152" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:25">
       <c r="C153" s="4" t="s">
         <v>17</v>
       </c>
@@ -6342,7 +6445,56 @@
         <v>-200</v>
       </c>
     </row>
-    <row r="155" spans="1:24">
+    <row r="154" spans="1:25">
+      <c r="E154">
+        <f>IF(E150=E152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="G154">
+        <f>IF(G150=G152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="I154">
+        <f>IF(I150=I152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="K154">
+        <f>IF(K150=K152,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <f>IF(M150=M152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="O154">
+        <f>IF(O150=O152,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q154">
+        <f>IF(Q150=Q152,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S154">
+        <f>IF(S150=S152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="U154">
+        <f>IF(U150=U152,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="W154">
+        <f>IF(W150=W152,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X154">
+        <f>SUM(E154:W154)</f>
+        <v>6</v>
+      </c>
+      <c r="Y154" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="155" spans="1:25">
       <c r="C155" s="4" t="s">
         <v>18</v>
       </c>
@@ -6391,7 +6543,7 @@
         <v>-10</v>
       </c>
     </row>
-    <row r="156" spans="1:24">
+    <row r="156" spans="1:25">
       <c r="C156" s="4" t="s">
         <v>19</v>
       </c>
@@ -6450,24 +6602,24 @@
         <v>7.1300000000000008</v>
       </c>
     </row>
-    <row r="157" spans="1:24">
+    <row r="157" spans="1:25">
       <c r="C157" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D157" s="5"/>
       <c r="E157" s="5">
         <f>IF(E152=E150,-E155+E156,0)</f>
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="F157" s="5"/>
       <c r="G157" s="5">
         <f>IF(G152=G150,-G155+G156,0)</f>
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="H157" s="5"/>
       <c r="I157" s="5">
         <f>IF(I152=I150,-I155+I156,0)</f>
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="J157" s="5"/>
       <c r="K157" s="5">
@@ -6477,7 +6629,7 @@
       <c r="L157" s="5"/>
       <c r="M157" s="5">
         <f>IF(M152=M150,-M155+M156,0)</f>
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="N157" s="5"/>
       <c r="O157" s="5">
@@ -6492,12 +6644,12 @@
       <c r="R157" s="5"/>
       <c r="S157" s="5">
         <f>IF(S152=S150,-S155+S156,0)</f>
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T157" s="5"/>
       <c r="U157" s="5">
         <f>IF(U152=U150,-U155+U156,0)</f>
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V157" s="5"/>
       <c r="W157" s="6">
@@ -6506,48 +6658,723 @@
       </c>
       <c r="X157" s="9">
         <f>SUM(E157:W157)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="1:24">
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="158" spans="1:25">
       <c r="X158" s="7">
         <f>X155+X157</f>
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="159" spans="1:24">
-      <c r="V159" s="13" t="s">
+        <v>-0.16000000000000014</v>
+      </c>
+    </row>
+    <row r="159" spans="1:25">
+      <c r="V159" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="W159" s="13"/>
+      <c r="W159" s="14"/>
       <c r="X159" s="11">
         <f>X140+X158</f>
-        <v>-10.879999999999999</v>
+        <v>-1.0399999999999991</v>
+      </c>
+    </row>
+    <row r="160" spans="1:25" ht="24">
+      <c r="E160" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="F160" s="13"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="13"/>
+      <c r="I160" s="13"/>
+      <c r="J160" s="13"/>
+      <c r="K160" s="13"/>
+      <c r="L160" s="13"/>
+      <c r="M160" s="13"/>
+      <c r="N160" s="13"/>
+      <c r="O160" s="13"/>
+      <c r="P160" s="13"/>
+      <c r="Q160" s="13"/>
+      <c r="R160" s="13"/>
+      <c r="S160" s="13"/>
+      <c r="T160" s="13"/>
+      <c r="U160" s="13"/>
+      <c r="V160" s="13"/>
+      <c r="W160" s="13"/>
+    </row>
+    <row r="161" spans="1:25">
+      <c r="A161" t="s">
+        <v>80</v>
+      </c>
+      <c r="E161" t="s">
+        <v>120</v>
+      </c>
+      <c r="G161" t="s">
+        <v>121</v>
+      </c>
+      <c r="I161" t="s">
+        <v>122</v>
+      </c>
+      <c r="K161" t="s">
+        <v>123</v>
+      </c>
+      <c r="M161" t="s">
+        <v>124</v>
+      </c>
+      <c r="O161" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q161" t="s">
+        <v>126</v>
+      </c>
+      <c r="S161" t="s">
+        <v>127</v>
+      </c>
+      <c r="U161" t="s">
+        <v>128</v>
+      </c>
+      <c r="W161" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="162" spans="1:25">
+      <c r="A162" t="s">
+        <v>91</v>
+      </c>
+      <c r="B162">
+        <v>3.5</v>
+      </c>
+      <c r="C162" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E162" t="s">
+        <v>13</v>
+      </c>
+      <c r="G162" t="s">
+        <v>13</v>
+      </c>
+      <c r="I162" t="s">
+        <v>13</v>
+      </c>
+      <c r="K162" t="s">
+        <v>13</v>
+      </c>
+      <c r="M162" t="s">
+        <v>13</v>
+      </c>
+      <c r="O162" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q162" t="s">
+        <v>13</v>
+      </c>
+      <c r="S162" t="s">
+        <v>13</v>
+      </c>
+      <c r="U162" t="s">
+        <v>13</v>
+      </c>
+      <c r="W162" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:25">
+      <c r="A163" t="s">
+        <v>91</v>
+      </c>
+      <c r="B163">
+        <v>2.5</v>
+      </c>
+      <c r="C163" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="E163" t="s">
+        <v>13</v>
+      </c>
+      <c r="G163" t="s">
+        <v>13</v>
+      </c>
+      <c r="I163" t="s">
+        <v>13</v>
+      </c>
+      <c r="K163" t="s">
+        <v>13</v>
+      </c>
+      <c r="M163" t="s">
+        <v>13</v>
+      </c>
+      <c r="O163" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q163" t="s">
+        <v>13</v>
+      </c>
+      <c r="S163" t="s">
+        <v>13</v>
+      </c>
+      <c r="U163" t="s">
+        <v>13</v>
+      </c>
+      <c r="W163" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164" spans="1:25">
+      <c r="A164" t="s">
+        <v>91</v>
+      </c>
+      <c r="B164">
+        <v>3.5</v>
+      </c>
+      <c r="C164" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E164" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" t="s">
+        <v>14</v>
+      </c>
+      <c r="I164" t="s">
+        <v>13</v>
+      </c>
+      <c r="K164" t="s">
+        <v>13</v>
+      </c>
+      <c r="M164" t="s">
+        <v>13</v>
+      </c>
+      <c r="O164" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q164" t="s">
+        <v>13</v>
+      </c>
+      <c r="S164" t="s">
+        <v>13</v>
+      </c>
+      <c r="U164" t="s">
+        <v>13</v>
+      </c>
+      <c r="W164" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165" spans="1:25">
+      <c r="A165" t="s">
+        <v>91</v>
+      </c>
+      <c r="B165">
+        <v>2.5</v>
+      </c>
+      <c r="C165" s="1">
+        <v>0.7</v>
+      </c>
+      <c r="E165" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" t="s">
+        <v>14</v>
+      </c>
+      <c r="I165" t="s">
+        <v>13</v>
+      </c>
+      <c r="K165" t="s">
+        <v>13</v>
+      </c>
+      <c r="M165" t="s">
+        <v>13</v>
+      </c>
+      <c r="O165" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>13</v>
+      </c>
+      <c r="S165" t="s">
+        <v>13</v>
+      </c>
+      <c r="U165" t="s">
+        <v>13</v>
+      </c>
+      <c r="W165" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166" spans="1:25">
+      <c r="A166" t="s">
+        <v>93</v>
+      </c>
+      <c r="B166">
+        <v>3.5</v>
+      </c>
+      <c r="E166" t="s">
+        <v>13</v>
+      </c>
+      <c r="G166" t="s">
+        <v>13</v>
+      </c>
+      <c r="I166" t="s">
+        <v>13</v>
+      </c>
+      <c r="K166" t="s">
+        <v>13</v>
+      </c>
+      <c r="M166" t="s">
+        <v>14</v>
+      </c>
+      <c r="O166" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q166" t="s">
+        <v>13</v>
+      </c>
+      <c r="S166" t="s">
+        <v>13</v>
+      </c>
+      <c r="U166" t="s">
+        <v>13</v>
+      </c>
+      <c r="W166" t="s">
+        <v>14</v>
+      </c>
+      <c r="X166" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="167" spans="1:25">
+      <c r="A167" t="s">
+        <v>93</v>
+      </c>
+      <c r="B167">
+        <v>2.5</v>
+      </c>
+      <c r="E167" t="s">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s">
+        <v>14</v>
+      </c>
+      <c r="I167" t="s">
+        <v>14</v>
+      </c>
+      <c r="K167" t="s">
+        <v>14</v>
+      </c>
+      <c r="M167" t="s">
+        <v>14</v>
+      </c>
+      <c r="O167" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q167" t="s">
+        <v>14</v>
+      </c>
+      <c r="S167" t="s">
+        <v>14</v>
+      </c>
+      <c r="U167" t="s">
+        <v>14</v>
+      </c>
+      <c r="W167" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="169" spans="1:25">
+      <c r="C169" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D169" s="5"/>
+      <c r="E169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="5"/>
+      <c r="G169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H169" s="5"/>
+      <c r="I169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="J169" s="5"/>
+      <c r="K169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L169" s="5"/>
+      <c r="M169" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="N169" s="5"/>
+      <c r="O169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="P169" s="5"/>
+      <c r="Q169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="R169" s="5"/>
+      <c r="S169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="T169" s="5"/>
+      <c r="U169" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="V169" s="5"/>
+      <c r="W169" s="6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="170" spans="1:25">
+      <c r="C170" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="5"/>
+      <c r="E170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="F170" s="5"/>
+      <c r="G170" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="H170" s="5"/>
+      <c r="I170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="J170" s="5"/>
+      <c r="K170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="L170" s="5"/>
+      <c r="M170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="N170" s="5"/>
+      <c r="O170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="P170" s="5"/>
+      <c r="Q170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="R170" s="5"/>
+      <c r="S170" s="5">
+        <v>3.5</v>
+      </c>
+      <c r="T170" s="5"/>
+      <c r="U170" s="5">
+        <v>2.5</v>
+      </c>
+      <c r="V170" s="5"/>
+      <c r="W170" s="6">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:25">
+      <c r="C171" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D171" s="5"/>
+      <c r="E171" s="5"/>
+      <c r="F171" s="5"/>
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+      <c r="I171" s="5"/>
+      <c r="J171" s="5"/>
+      <c r="K171" s="5"/>
+      <c r="L171" s="5"/>
+      <c r="M171" s="5"/>
+      <c r="N171" s="5"/>
+      <c r="O171" s="5"/>
+      <c r="P171" s="5"/>
+      <c r="Q171" s="5"/>
+      <c r="R171" s="5"/>
+      <c r="S171" s="5"/>
+      <c r="T171" s="5"/>
+      <c r="U171" s="5"/>
+      <c r="V171" s="5"/>
+      <c r="W171" s="6"/>
+    </row>
+    <row r="172" spans="1:25">
+      <c r="C172" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D172" s="5"/>
+      <c r="E172" s="5"/>
+      <c r="F172" s="5"/>
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+      <c r="I172" s="5"/>
+      <c r="J172" s="5"/>
+      <c r="K172" s="5"/>
+      <c r="L172" s="5"/>
+      <c r="M172" s="5"/>
+      <c r="N172" s="5"/>
+      <c r="O172" s="5"/>
+      <c r="P172" s="5"/>
+      <c r="Q172" s="5"/>
+      <c r="R172" s="5"/>
+      <c r="S172" s="5"/>
+      <c r="T172" s="5"/>
+      <c r="U172" s="5"/>
+      <c r="V172" s="5"/>
+      <c r="W172" s="6"/>
+    </row>
+    <row r="173" spans="1:25">
+      <c r="E173">
+        <f>IF(E169=E171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <f>IF(G169=G171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <f>IF(I169=I171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <f>IF(K169=K171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <f>IF(M169=M171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <f>IF(O169=O171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q173">
+        <f>IF(Q169=Q171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S173">
+        <f>IF(S169=S171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="U173">
+        <f>IF(U169=U171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="W173">
+        <f>IF(W169=W171,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X173">
+        <f>SUM(E173:W173)</f>
+        <v>0</v>
+      </c>
+      <c r="Y173" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="174" spans="1:25">
+      <c r="C174" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D174" s="5"/>
+      <c r="E174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="F174" s="5"/>
+      <c r="G174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="H174" s="5"/>
+      <c r="I174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="J174" s="5"/>
+      <c r="K174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="L174" s="5"/>
+      <c r="M174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="N174" s="5"/>
+      <c r="O174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="P174" s="5"/>
+      <c r="Q174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="R174" s="5"/>
+      <c r="S174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="T174" s="5"/>
+      <c r="U174" s="5">
+        <v>-1</v>
+      </c>
+      <c r="V174" s="5"/>
+      <c r="W174" s="6">
+        <v>-1</v>
+      </c>
+      <c r="X174" s="8">
+        <f>SUM(E174:W174)</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="175" spans="1:25">
+      <c r="C175" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D175" s="5"/>
+      <c r="E175" s="5" t="e">
+        <f>IF(E172&gt;0,ROUND(ABS(E174)*(E172/100),2),ROUND(E174/(E172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="F175" s="5"/>
+      <c r="G175" s="5" t="e">
+        <f>IF(G172&gt;0,ROUND(ABS(G174)*(G172/100),2),ROUND(G174/(G172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H175" s="5"/>
+      <c r="I175" s="5" t="e">
+        <f>IF(I172&gt;0,ROUND(ABS(I174)*(I172/100),2),ROUND(I174/(I172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="J175" s="5"/>
+      <c r="K175" s="5" t="e">
+        <f>IF(K172&gt;0,ROUND(ABS(K174)*(K172/100),2),ROUND(K174/(K172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="L175" s="5"/>
+      <c r="M175" s="5" t="e">
+        <f>IF(M172&gt;0,ROUND(ABS(M174)*(M172/100),2),ROUND(M174/(M172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N175" s="5"/>
+      <c r="O175" s="5" t="e">
+        <f>IF(O172&gt;0,ROUND(ABS(O174)*(O172/100),2),ROUND(O174/(O172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P175" s="5"/>
+      <c r="Q175" s="5" t="e">
+        <f>IF(Q172&gt;0,ROUND(ABS(Q174)*(Q172/100),2),ROUND(Q174/(Q172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R175" s="5"/>
+      <c r="S175" s="5" t="e">
+        <f>IF(S172&gt;0,ROUND(ABS(S174)*(S172/100),2),ROUND(S174/(S172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T175" s="5"/>
+      <c r="U175" s="5" t="e">
+        <f>IF(U172&gt;0,ROUND(ABS(U174)*(U172/100),2),ROUND(U174/(U172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V175" s="5"/>
+      <c r="W175" s="5" t="e">
+        <f>IF(W172&gt;0,ROUND(ABS(W174)*(W172/100),2),ROUND(W174/(W172/100),2))</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="X175" s="8" t="e">
+        <f>SUM(E175:W175)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="176" spans="1:25">
+      <c r="C176" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D176" s="5"/>
+      <c r="E176" s="5">
+        <f>IF(E171=E169,-E174+E175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="F176" s="5"/>
+      <c r="G176" s="5">
+        <f>IF(G171=G169,-G174+G175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="H176" s="5"/>
+      <c r="I176" s="5">
+        <f>IF(I171=I169,-I174+I175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="J176" s="5"/>
+      <c r="K176" s="5">
+        <f>IF(K171=K169,-K174+K175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="L176" s="5"/>
+      <c r="M176" s="5">
+        <f>IF(M171=M169,-M174+M175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="N176" s="5"/>
+      <c r="O176" s="5">
+        <f>IF(O171=O169,-O174+O175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P176" s="5"/>
+      <c r="Q176" s="5">
+        <f>IF(Q171=Q169,-Q174+Q175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R176" s="5"/>
+      <c r="S176" s="5">
+        <f>IF(S171=S169,-S174+S175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T176" s="5"/>
+      <c r="U176" s="5">
+        <f>IF(U171=U169,-U174+U175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="V176" s="5"/>
+      <c r="W176" s="6">
+        <f>IF(W171=W169,-W174+W175,0)</f>
+        <v>0</v>
+      </c>
+      <c r="X176" s="9">
+        <f>SUM(E176:W176)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="22:24">
+      <c r="X177" s="7">
+        <f>X174+X176</f>
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="178" spans="22:24">
+      <c r="V178" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="W178" s="14"/>
+      <c r="X178" s="11">
+        <f>X159+X177</f>
+        <v>-11.04</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="Y105:Z110"/>
-    <mergeCell ref="E122:W122"/>
-    <mergeCell ref="V140:W140"/>
-    <mergeCell ref="E103:W103"/>
-    <mergeCell ref="V121:W121"/>
-    <mergeCell ref="E1:W1"/>
-    <mergeCell ref="E18:W18"/>
-    <mergeCell ref="E35:W35"/>
-    <mergeCell ref="V17:W17"/>
-    <mergeCell ref="V34:W34"/>
-    <mergeCell ref="E69:W69"/>
-    <mergeCell ref="V85:W85"/>
-    <mergeCell ref="E52:W52"/>
-    <mergeCell ref="V68:W68"/>
-    <mergeCell ref="V51:W51"/>
+  <mergeCells count="23">
+    <mergeCell ref="E160:W160"/>
+    <mergeCell ref="V178:W178"/>
     <mergeCell ref="E141:W141"/>
     <mergeCell ref="V159:W159"/>
     <mergeCell ref="E125:W125"/>
     <mergeCell ref="E127:W127"/>
     <mergeCell ref="E86:W86"/>
     <mergeCell ref="V102:W102"/>
+    <mergeCell ref="E69:W69"/>
+    <mergeCell ref="V85:W85"/>
+    <mergeCell ref="E52:W52"/>
+    <mergeCell ref="V68:W68"/>
+    <mergeCell ref="V51:W51"/>
+    <mergeCell ref="E1:W1"/>
+    <mergeCell ref="E18:W18"/>
+    <mergeCell ref="E35:W35"/>
+    <mergeCell ref="V17:W17"/>
+    <mergeCell ref="V34:W34"/>
+    <mergeCell ref="Y105:Z110"/>
+    <mergeCell ref="E122:W122"/>
+    <mergeCell ref="V140:W140"/>
+    <mergeCell ref="E103:W103"/>
+    <mergeCell ref="V121:W121"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
